--- a/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
@@ -12560,7 +12560,7 @@
         <v>4.588024027153121</v>
       </c>
       <c r="F434" t="n">
-        <v>4.45898767581001</v>
+        <v>4.455509411433685</v>
       </c>
       <c r="G434" t="n">
         <v>4.508659285607248</v>
@@ -12591,7 +12591,7 @@
         <v>4.582924577040772</v>
       </c>
       <c r="F435" t="n">
-        <v>4.468204330914934</v>
+        <v>4.464758032271346</v>
       </c>
       <c r="G435" t="n">
         <v>4.576770711466393</v>
@@ -12624,7 +12624,7 @@
         <v>4.58700621536042</v>
       </c>
       <c r="F436" t="n">
-        <v>4.515245478460105</v>
+        <v>4.513054897080286</v>
       </c>
       <c r="G436" t="n">
         <v>4.55597994179732</v>
@@ -12655,7 +12655,7 @@
         <v>4.602165676967792</v>
       </c>
       <c r="F437" t="n">
-        <v>4.540098189244376</v>
+        <v>4.536891345234797</v>
       </c>
       <c r="G437" t="n">
         <v>4.561218298458908</v>
@@ -12686,7 +12686,7 @@
         <v>4.58700621536042</v>
       </c>
       <c r="F438" t="n">
-        <v>4.566429357671661</v>
+        <v>4.563305981889393</v>
       </c>
       <c r="G438" t="n">
         <v>4.613138355637268</v>
@@ -12719,7 +12719,7 @@
         <v>4.604169685654508</v>
       </c>
       <c r="F439" t="n">
-        <v>4.594109238628667</v>
+        <v>4.593097604753822</v>
       </c>
       <c r="G439" t="n">
         <v>4.627909672957581</v>
@@ -12845,7 +12845,7 @@
         <v>4.606169686321175</v>
       </c>
       <c r="F443" t="n">
-        <v>4.683981366412381</v>
+        <v>4.68213122712422</v>
       </c>
       <c r="G443" t="n">
         <v>4.648229675448539</v>
@@ -12876,7 +12876,7 @@
         <v>4.626931677769604</v>
       </c>
       <c r="F444" t="n">
-        <v>4.679349584162343</v>
+        <v>4.677490847567717</v>
       </c>
       <c r="G444" t="n">
         <v>4.623991940228679</v>
@@ -12940,7 +12940,7 @@
         <v>4.562262684976814</v>
       </c>
       <c r="F446" t="n">
-        <v>4.730039168033961</v>
+        <v>4.727387818712341</v>
       </c>
       <c r="G446" t="n">
         <v>4.609162207257629</v>
@@ -12971,7 +12971,7 @@
         <v>4.616110126026426</v>
       </c>
       <c r="F447" t="n">
-        <v>4.768139014266231</v>
+        <v>4.765586907393996</v>
       </c>
       <c r="G447" t="n">
         <v>4.617098756853365</v>
@@ -13004,7 +13004,7 @@
         <v>4.620058798481842</v>
       </c>
       <c r="F448" t="n">
-        <v>4.784988612563928</v>
+        <v>4.783316371371566</v>
       </c>
       <c r="G448" t="n">
         <v>4.614129927359564</v>
@@ -13035,7 +13035,7 @@
         <v>4.639571612705423</v>
       </c>
       <c r="F449" t="n">
-        <v>4.799914262780603</v>
+        <v>4.796616650559047</v>
       </c>
       <c r="G449" t="n">
         <v>4.612145799724517</v>
@@ -13066,7 +13066,7 @@
         <v>4.618086411254637</v>
       </c>
       <c r="F450" t="n">
-        <v>4.815431111471288</v>
+        <v>4.811371016571989</v>
       </c>
       <c r="G450" t="n">
         <v>4.642465970731788</v>
@@ -13099,7 +13099,7 @@
         <v>4.596129441335942</v>
       </c>
       <c r="F451" t="n">
-        <v>4.799914262780603</v>
+        <v>4.799090878625398</v>
       </c>
       <c r="G451" t="n">
         <v>4.611152257665639</v>
@@ -13130,7 +13130,7 @@
         <v>4.601162164590552</v>
       </c>
       <c r="F452" t="n">
-        <v>4.801558999993482</v>
+        <v>4.800736969532067</v>
       </c>
       <c r="G452" t="n">
         <v>4.61512051684126</v>
@@ -13225,7 +13225,7 @@
         <v>4.590056548178043</v>
       </c>
       <c r="F455" t="n">
-        <v>4.825108606353353</v>
+        <v>4.823502180305079</v>
       </c>
       <c r="G455" t="n">
         <v>4.604169685654508</v>
@@ -13256,7 +13256,7 @@
         <v>4.588024027153121</v>
       </c>
       <c r="F456" t="n">
-        <v>4.817859279398442</v>
+        <v>4.817050545023591</v>
       </c>
       <c r="G456" t="n">
         <v>4.607168188650764</v>
@@ -13289,7 +13289,7 @@
         <v>4.601162164590552</v>
       </c>
       <c r="F457" t="n">
-        <v>4.832305758571839</v>
+        <v>4.830710861902022</v>
       </c>
       <c r="G457" t="n">
         <v>4.597138014290827</v>
@@ -13320,7 +13320,7 @@
         <v>4.590056548178043</v>
       </c>
       <c r="F458" t="n">
-        <v>4.819474788635096</v>
+        <v>4.817859279398442</v>
       </c>
       <c r="G458" t="n">
         <v>4.604169685654508</v>
@@ -13351,7 +13351,7 @@
         <v>4.599152113662528</v>
       </c>
       <c r="F459" t="n">
-        <v>4.838660029356445</v>
+        <v>4.836281906951478</v>
       </c>
       <c r="G459" t="n">
         <v>4.596129441335942</v>
@@ -13384,7 +13384,7 @@
         <v>4.592084946439436</v>
       </c>
       <c r="F460" t="n">
-        <v>4.850466541943434</v>
+        <v>4.848900370910689</v>
       </c>
       <c r="G460" t="n">
         <v>4.59511985013459</v>
@@ -13415,7 +13415,7 @@
         <v>4.571613402459248</v>
       </c>
       <c r="F461" t="n">
-        <v>4.825108606353353</v>
+        <v>4.821087692210561</v>
       </c>
       <c r="G461" t="n">
         <v>4.591071261608589</v>
@@ -13446,7 +13446,7 @@
         <v>4.585987366571318</v>
       </c>
       <c r="F462" t="n">
-        <v>4.830710861902022</v>
+        <v>4.827513417131532</v>
       </c>
       <c r="G462" t="n">
         <v>4.594109238628667</v>
@@ -13479,7 +13479,7 @@
         <v>4.588024027153121</v>
       </c>
       <c r="F463" t="n">
-        <v>4.8629083820668</v>
+        <v>4.862135285777812</v>
       </c>
       <c r="G463" t="n">
         <v>4.588024027153121</v>
@@ -13510,7 +13510,7 @@
         <v>4.579852378003801</v>
       </c>
       <c r="F464" t="n">
-        <v>4.866764923676554</v>
+        <v>4.86599480426999</v>
       </c>
       <c r="G464" t="n">
         <v>4.58700621536042</v>
@@ -13541,7 +13541,7 @@
         <v>4.58700621536042</v>
       </c>
       <c r="F465" t="n">
-        <v>4.906755163608864</v>
+        <v>4.906015244966153</v>
       </c>
       <c r="G465" t="n">
         <v>4.582924577040772</v>
@@ -13605,7 +13605,7 @@
         <v>4.582924577040772</v>
       </c>
       <c r="F467" t="n">
-        <v>4.897839799950911</v>
+        <v>4.897093252697127</v>
       </c>
       <c r="G467" t="n">
         <v>4.580877493419047</v>
@@ -13636,7 +13636,7 @@
         <v>4.562262684976814</v>
       </c>
       <c r="F468" t="n">
-        <v>4.907494535176743</v>
+        <v>4.906015244966153</v>
       </c>
       <c r="G468" t="n">
         <v>4.583946549536464</v>
@@ -13669,7 +13669,7 @@
         <v>4.585987366571318</v>
       </c>
       <c r="F469" t="n">
-        <v>4.954417614098027</v>
+        <v>4.952299717083292</v>
       </c>
       <c r="G469" t="n">
         <v>4.575741375297279</v>
@@ -13700,7 +13700,7 @@
         <v>4.553876891600541</v>
       </c>
       <c r="F470" t="n">
-        <v>4.930870325627393</v>
+        <v>4.92870191133357</v>
       </c>
       <c r="G470" t="n">
         <v>4.580877493419047</v>
@@ -13731,7 +13731,7 @@
         <v>4.564348191467836</v>
       </c>
       <c r="F471" t="n">
-        <v>4.92870191133357</v>
+        <v>4.925803358579558</v>
       </c>
       <c r="G471" t="n">
         <v>4.581901559048737</v>
@@ -13764,7 +13764,7 @@
         <v>4.55597994179732</v>
       </c>
       <c r="F472" t="n">
-        <v>4.883559211528279</v>
+        <v>4.880526608749236</v>
       </c>
       <c r="G472" t="n">
         <v>4.583946549536464</v>
@@ -13795,7 +13795,7 @@
         <v>4.544358046591334</v>
       </c>
       <c r="F473" t="n">
-        <v>4.90527477843843</v>
+        <v>4.902307417210627</v>
       </c>
       <c r="G473" t="n">
         <v>4.579852378003801</v>
@@ -13826,7 +13826,7 @@
         <v>4.545420181582317</v>
       </c>
       <c r="F474" t="n">
-        <v>4.897093252697127</v>
+        <v>4.894101477840304</v>
       </c>
       <c r="G474" t="n">
         <v>4.582924577040772</v>
@@ -13859,7 +13859,7 @@
         <v>4.549657476057832</v>
       </c>
       <c r="F475" t="n">
-        <v>4.902307417210627</v>
+        <v>4.900820428089049</v>
       </c>
       <c r="G475" t="n">
         <v>4.578826210648489</v>
@@ -13890,7 +13890,7 @@
         <v>4.535820107853298</v>
       </c>
       <c r="F476" t="n">
-        <v>4.90527477843843</v>
+        <v>4.906015244966153</v>
       </c>
       <c r="G476" t="n">
         <v>4.582924577040772</v>
@@ -13954,7 +13954,7 @@
         <v>4.532599493153256</v>
       </c>
       <c r="F478" t="n">
-        <v>4.90453376321371</v>
+        <v>4.903050083416319</v>
       </c>
       <c r="G478" t="n">
         <v>4.591071261608589</v>
@@ -13985,7 +13985,7 @@
         <v>4.539030383483547</v>
       </c>
       <c r="F479" t="n">
-        <v>4.895598484107897</v>
+        <v>4.894850261102546</v>
       </c>
       <c r="G479" t="n">
         <v>4.583946549536464</v>
@@ -14016,7 +14016,7 @@
         <v>4.541164856012179</v>
       </c>
       <c r="F480" t="n">
-        <v>4.93662988078576</v>
+        <v>4.934473933130691</v>
       </c>
       <c r="G480" t="n">
         <v>4.576770711466393</v>
@@ -14049,7 +14049,7 @@
         <v>4.517431271680085</v>
       </c>
       <c r="F481" t="n">
-        <v>4.900820428089049</v>
+        <v>4.899331224537582</v>
       </c>
       <c r="G481" t="n">
         <v>4.584967478670572</v>
@@ -14080,7 +14080,7 @@
         <v>4.543294782270004</v>
       </c>
       <c r="F482" t="n">
-        <v>4.944495491591711</v>
+        <v>4.942356453342962</v>
       </c>
       <c r="G482" t="n">
         <v>4.577798989191959</v>
@@ -14111,7 +14111,7 @@
         <v>4.534747721691546</v>
       </c>
       <c r="F483" t="n">
-        <v>4.932313327320786</v>
+        <v>4.929425238670713</v>
       </c>
       <c r="G483" t="n">
         <v>4.578826210648489</v>
@@ -14144,7 +14144,7 @@
         <v>4.533674184283021</v>
       </c>
       <c r="F484" t="n">
-        <v>4.93014804318357</v>
+        <v>4.927253685157205</v>
       </c>
       <c r="G484" t="n">
         <v>4.573679518896721</v>
@@ -14175,7 +14175,7 @@
         <v>4.541164856012179</v>
       </c>
       <c r="F485" t="n">
-        <v>4.935911747900319</v>
+        <v>4.932313327320786</v>
       </c>
       <c r="G485" t="n">
         <v>4.580877493419047</v>
@@ -14206,7 +14206,7 @@
         <v>4.536891345234797</v>
       </c>
       <c r="F486" t="n">
-        <v>4.938781190328272</v>
+        <v>4.934473933130691</v>
       </c>
       <c r="G486" t="n">
         <v>4.578826210648489</v>
@@ -14239,7 +14239,7 @@
         <v>4.543294782270004</v>
       </c>
       <c r="F487" t="n">
-        <v>4.93806460126142</v>
+        <v>4.93662988078576</v>
       </c>
       <c r="G487" t="n">
         <v>4.581901559048737</v>
@@ -14270,7 +14270,7 @@
         <v>4.546481189639412</v>
       </c>
       <c r="F488" t="n">
-        <v>4.94021282979971</v>
+        <v>4.940927881671436</v>
       </c>
       <c r="G488" t="n">
         <v>4.583946549536464</v>
@@ -14301,7 +14301,7 @@
         <v>4.525044141508807</v>
       </c>
       <c r="F489" t="n">
-        <v>4.927978060415247</v>
+        <v>4.926528784799256</v>
       </c>
       <c r="G489" t="n">
         <v>4.578826210648489</v>
@@ -14396,7 +14396,7 @@
         <v>4.550714000192032</v>
       </c>
       <c r="F492" t="n">
-        <v>4.958639998977875</v>
+        <v>4.956531035103055</v>
       </c>
       <c r="G492" t="n">
         <v>4.585987366571318</v>
@@ -14429,7 +14429,7 @@
         <v>4.545420181582317</v>
       </c>
       <c r="F493" t="n">
-        <v>4.950885289690482</v>
+        <v>4.949468858858769</v>
       </c>
       <c r="G493" t="n">
         <v>4.581901559048737</v>
@@ -14460,7 +14460,7 @@
         <v>4.539030383483547</v>
       </c>
       <c r="F494" t="n">
-        <v>4.940927881671436</v>
+        <v>4.93806460126142</v>
       </c>
       <c r="G494" t="n">
         <v>4.583946549536464</v>
@@ -14491,7 +14491,7 @@
         <v>4.540098189244376</v>
       </c>
       <c r="F495" t="n">
-        <v>4.940927881671436</v>
+        <v>4.93806460126142</v>
       </c>
       <c r="G495" t="n">
         <v>4.583946549536464</v>
@@ -14524,7 +14524,7 @@
         <v>4.546481189639412</v>
       </c>
       <c r="F496" t="n">
-        <v>4.959341999708705</v>
+        <v>4.956531035103055</v>
       </c>
       <c r="G496" t="n">
         <v>4.58700621536042</v>
@@ -14555,7 +14555,7 @@
         <v>4.550714000192032</v>
       </c>
       <c r="F497" t="n">
-        <v>4.967031656614123</v>
+        <v>4.963543686562405</v>
       </c>
       <c r="G497" t="n">
         <v>4.58700621536042</v>
@@ -14586,7 +14586,7 @@
         <v>4.548599834499697</v>
       </c>
       <c r="F498" t="n">
-        <v>4.967031656614123</v>
+        <v>4.964242254526545</v>
       </c>
       <c r="G498" t="n">
         <v>4.583946549536464</v>
@@ -14618,7 +14618,9 @@
       <c r="E499" t="n">
         <v>4.537961436294641</v>
       </c>
-      <c r="F499" t="inlineStr"/>
+      <c r="F499" t="n">
+        <v>4.94306997460049</v>
+      </c>
       <c r="G499" t="n">
         <v>4.583946549536464</v>
       </c>
@@ -14647,7 +14649,9 @@
       <c r="E500" t="n">
         <v>4.545420181582317</v>
       </c>
-      <c r="F500" t="inlineStr"/>
+      <c r="F500" t="n">
+        <v>4.92870191133357</v>
+      </c>
       <c r="G500" t="n">
         <v>4.580877493419047</v>
       </c>

--- a/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K501"/>
+  <dimension ref="A1:K502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4193,7 +4193,7 @@
         <v>3.37</v>
       </c>
       <c r="D169" t="n">
-        <v>4.643428898105181</v>
+        <v>4.644390899141372</v>
       </c>
       <c r="E169" t="n">
         <v>4.73356340075649</v>
@@ -5462,7 +5462,7 @@
         <v>3.4671364</v>
       </c>
       <c r="D210" t="n">
-        <v>4.671893818030999</v>
+        <v>4.670957926526095</v>
       </c>
       <c r="E210" t="n">
         <v>4.78164132910387</v>
@@ -6381,7 +6381,7 @@
         <v>2.1473333</v>
       </c>
       <c r="D239" t="n">
-        <v>4.628886712605407</v>
+        <v>4.629862798578463</v>
       </c>
       <c r="E239" t="n">
         <v>4.766438333584214</v>
@@ -7046,7 +7046,7 @@
         <v>3.1021905</v>
       </c>
       <c r="D260" t="n">
-        <v>4.707726774313183</v>
+        <v>4.706823839714591</v>
       </c>
       <c r="E260" t="n">
         <v>4.783316371371566</v>
@@ -7552,7 +7552,7 @@
         <v>4.6385455</v>
       </c>
       <c r="D276" t="n">
-        <v>4.643428898105181</v>
+        <v>4.644390899141372</v>
       </c>
       <c r="E276" t="n">
         <v>4.795790545596741</v>
@@ -10371,7 +10371,7 @@
         <v>0.0047</v>
       </c>
       <c r="D365" t="n">
-        <v>4.623991940228679</v>
+        <v>4.623010104116422</v>
       </c>
       <c r="E365" t="n">
         <v>4.553876891600541</v>
@@ -13188,7 +13188,7 @@
         <v>1.0108636</v>
       </c>
       <c r="D454" t="n">
-        <v>4.559126247486684</v>
+        <v>4.560172820057356</v>
       </c>
       <c r="E454" t="n">
         <v>4.602165676967792</v>
@@ -13725,7 +13725,7 @@
         <v>3.9231905</v>
       </c>
       <c r="D471" t="n">
-        <v>4.596129441335942</v>
+        <v>4.59511985013459</v>
       </c>
       <c r="E471" t="n">
         <v>4.564348191467836</v>
@@ -14138,7 +14138,7 @@
         <v>2.4424286</v>
       </c>
       <c r="D484" t="n">
-        <v>4.581901559048737</v>
+        <v>4.580877493419047</v>
       </c>
       <c r="E484" t="n">
         <v>4.533674184283021</v>
@@ -14328,7 +14328,7 @@
         <v>2.0272727</v>
       </c>
       <c r="D490" t="n">
-        <v>4.597138014290827</v>
+        <v>4.598145571051127</v>
       </c>
       <c r="E490" t="n">
         <v>4.547541073151455</v>
@@ -14359,7 +14359,7 @@
         <v>2.0344348</v>
       </c>
       <c r="D491" t="n">
-        <v>4.611152257665639</v>
+        <v>4.612145799724517</v>
       </c>
       <c r="E491" t="n">
         <v>4.537961436294641</v>
@@ -14423,7 +14423,7 @@
         <v>2.0484286</v>
       </c>
       <c r="D493" t="n">
-        <v>4.617098756853365</v>
+        <v>4.616110126026426</v>
       </c>
       <c r="E493" t="n">
         <v>4.545420181582317</v>
@@ -14518,7 +14518,7 @@
         <v>2.1094091</v>
       </c>
       <c r="D496" t="n">
-        <v>4.612145799724517</v>
+        <v>4.611152257665639</v>
       </c>
       <c r="E496" t="n">
         <v>4.546481189639412</v>
@@ -14549,7 +14549,7 @@
         <v>2.1753</v>
       </c>
       <c r="D497" t="n">
-        <v>4.584967478670572</v>
+        <v>4.583946549536464</v>
       </c>
       <c r="E497" t="n">
         <v>4.550714000192032</v>
@@ -14613,7 +14613,7 @@
         <v>2.339</v>
       </c>
       <c r="D499" t="n">
-        <v>4.599152113662528</v>
+        <v>4.598145571051127</v>
       </c>
       <c r="E499" t="n">
         <v>4.537961436294641</v>
@@ -14644,7 +14644,7 @@
         <v>2.4253913</v>
       </c>
       <c r="D500" t="n">
-        <v>4.602165676967792</v>
+        <v>4.601162164590552</v>
       </c>
       <c r="E500" t="n">
         <v>4.545420181582317</v>
@@ -14675,7 +14675,7 @@
         <v>2.5131429</v>
       </c>
       <c r="D501" t="n">
-        <v>4.61015772749913</v>
+        <v>4.611152257665639</v>
       </c>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr"/>
@@ -14689,6 +14689,23 @@
       </c>
       <c r="K501" t="inlineStr"/>
     </row>
+    <row r="502">
+      <c r="A502" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="n">
+        <v>4.603168183317418</v>
+      </c>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr"/>
+      <c r="I502" t="inlineStr"/>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
@@ -14694,7 +14694,9 @@
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>
-      <c r="C502" t="inlineStr"/>
+      <c r="C502" t="n">
+        <v>2.6350455</v>
+      </c>
       <c r="D502" t="n">
         <v>4.603168183317418</v>
       </c>

--- a/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
@@ -10257,7 +10257,7 @@
         <v>4.599152113662528</v>
       </c>
       <c r="H361" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="I361" t="n">
         <v>4.39197696552705</v>
@@ -11238,7 +11238,7 @@
         <v>4.603168183317418</v>
       </c>
       <c r="H392" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="I392" t="n">
         <v>4.388257184424518</v>
@@ -12281,7 +12281,7 @@
         <v>4.239886867512759</v>
       </c>
       <c r="H425" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I425" t="n">
         <v>4.428433007488037</v>
@@ -12597,7 +12597,7 @@
         <v>4.576770711466393</v>
       </c>
       <c r="H435" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="I435" t="n">
         <v>4.411585436915426</v>
@@ -12977,7 +12977,7 @@
         <v>4.617098756853365</v>
       </c>
       <c r="H447" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I447" t="n">
         <v>4.471638793363569</v>
@@ -13167,7 +13167,7 @@
         <v>4.613138355637268</v>
       </c>
       <c r="H453" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I453" t="n">
         <v>4.516338972281476</v>
@@ -14212,7 +14212,7 @@
         <v>4.578826210648489</v>
       </c>
       <c r="H486" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="I486" t="n">
         <v>4.609162207257629</v>
@@ -14307,7 +14307,7 @@
         <v>4.578826210648489</v>
       </c>
       <c r="H489" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I489" t="n">
         <v>4.600157644164547</v>
@@ -14530,7 +14530,7 @@
         <v>4.58700621536042</v>
       </c>
       <c r="H496" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I496" t="n">
         <v>4.622027303054514</v>
@@ -14561,7 +14561,7 @@
         <v>4.58700621536042</v>
       </c>
       <c r="H497" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I497" t="n">
         <v>4.637637376125593</v>
@@ -14592,7 +14592,7 @@
         <v>4.583946549536464</v>
       </c>
       <c r="H498" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I498" t="n">
         <v>4.640537329825382</v>
@@ -14625,7 +14625,7 @@
         <v>4.583946549536464</v>
       </c>
       <c r="H499" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I499" t="n">
         <v>4.640537329825382</v>
@@ -14656,7 +14656,7 @@
         <v>4.580877493419047</v>
       </c>
       <c r="H500" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I500" t="n">
         <v>4.630837932736669</v>
@@ -14680,7 +14680,9 @@
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr"/>
       <c r="G501" t="inlineStr"/>
-      <c r="H501" t="inlineStr"/>
+      <c r="H501" t="n">
+        <v>6.2</v>
+      </c>
       <c r="I501" t="n">
         <v>4.631812116934513</v>
       </c>

--- a/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
@@ -4775,7 +4775,7 @@
         <v>4.705920089088234</v>
       </c>
       <c r="G188" t="n">
-        <v>4.674696248636701</v>
+        <v>4.675628649636653</v>
       </c>
       <c r="H188" t="n">
         <v>10</v>
@@ -5345,7 +5345,7 @@
         <v>4.798266815950004</v>
       </c>
       <c r="G206" t="n">
-        <v>4.715816706075155</v>
+        <v>4.716711560720999</v>
       </c>
       <c r="H206" t="n">
         <v>8.6</v>
@@ -7024,7 +7024,7 @@
         <v>4.871373226762748</v>
       </c>
       <c r="G259" t="n">
-        <v>4.69866052907543</v>
+        <v>4.697749367281185</v>
       </c>
       <c r="H259" t="n">
         <v>6.8</v>
@@ -8100,7 +8100,7 @@
         <v>4.839451481712757</v>
       </c>
       <c r="G293" t="n">
-        <v>4.65586330030361</v>
+        <v>4.65681341913993</v>
       </c>
       <c r="H293" t="n">
         <v>7.5</v>
@@ -9810,7 +9810,7 @@
         <v>4.479606963012746</v>
       </c>
       <c r="G347" t="n">
-        <v>4.580877493419047</v>
+        <v>4.581901559048737</v>
       </c>
       <c r="H347" t="n">
         <v>12.5</v>
@@ -12309,7 +12309,7 @@
         <v>4.289088639014612</v>
       </c>
       <c r="G426" t="n">
-        <v>4.45318382899021</v>
+        <v>4.452019006493916</v>
       </c>
       <c r="H426" t="n">
         <v>8.800000000000001</v>
@@ -13767,7 +13767,7 @@
         <v>4.880526608749236</v>
       </c>
       <c r="G472" t="n">
-        <v>4.583946549536464</v>
+        <v>4.582924577040772</v>
       </c>
       <c r="H472" t="n">
         <v>6.9</v>
@@ -13924,7 +13924,7 @@
         <v>4.903050083416319</v>
       </c>
       <c r="G477" t="n">
-        <v>4.584967478670572</v>
+        <v>4.583946549536464</v>
       </c>
       <c r="H477" t="n">
         <v>6.4</v>
@@ -14304,7 +14304,7 @@
         <v>4.926528784799256</v>
       </c>
       <c r="G489" t="n">
-        <v>4.578826210648489</v>
+        <v>4.579852378003801</v>
       </c>
       <c r="H489" t="n">
         <v>5.7</v>
@@ -14494,7 +14494,7 @@
         <v>4.93806460126142</v>
       </c>
       <c r="G495" t="n">
-        <v>4.583946549536464</v>
+        <v>4.582924577040772</v>
       </c>
       <c r="H495" t="n">
         <v>5.6</v>
@@ -14558,7 +14558,7 @@
         <v>4.963543686562405</v>
       </c>
       <c r="G497" t="n">
-        <v>4.58700621536042</v>
+        <v>4.585987366571318</v>
       </c>
       <c r="H497" t="n">
         <v>5.6</v>
@@ -14589,7 +14589,7 @@
         <v>4.964242254526545</v>
       </c>
       <c r="G498" t="n">
-        <v>4.583946549536464</v>
+        <v>4.581901559048737</v>
       </c>
       <c r="H498" t="n">
         <v>5.6</v>
@@ -14653,7 +14653,7 @@
         <v>4.92870191133357</v>
       </c>
       <c r="G500" t="n">
-        <v>4.580877493419047</v>
+        <v>4.579852378003801</v>
       </c>
       <c r="H500" t="n">
         <v>6</v>
@@ -14679,7 +14679,9 @@
       </c>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr"/>
-      <c r="G501" t="inlineStr"/>
+      <c r="G501" t="n">
+        <v>4.580877493419047</v>
+      </c>
       <c r="H501" t="n">
         <v>6.2</v>
       </c>
@@ -14706,7 +14708,9 @@
       <c r="F502" t="inlineStr"/>
       <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr"/>
-      <c r="I502" t="inlineStr"/>
+      <c r="I502" t="n">
+        <v>4.652053771886941</v>
+      </c>
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr"/>
     </row>

--- a/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
@@ -3274,7 +3274,7 @@
         <v>35155</v>
       </c>
       <c r="B136" t="n">
-        <v>12.906642460057</v>
+        <v>12.89210129939212</v>
       </c>
       <c r="C136" t="n">
         <v>5.5</v>
@@ -3357,7 +3357,7 @@
         <v>35246</v>
       </c>
       <c r="B139" t="n">
-        <v>12.90808144570034</v>
+        <v>12.8929346154706</v>
       </c>
       <c r="C139" t="n">
         <v>5.08</v>
@@ -3440,7 +3440,7 @@
         <v>35338</v>
       </c>
       <c r="B142" t="n">
-        <v>12.90983849791014</v>
+        <v>12.89474683717418</v>
       </c>
       <c r="C142" t="n">
         <v>4.86</v>
@@ -3523,7 +3523,7 @@
         <v>35430</v>
       </c>
       <c r="B145" t="n">
-        <v>12.90656627473306</v>
+        <v>12.89119118261244</v>
       </c>
       <c r="C145" t="n">
         <v>4.5</v>
@@ -3606,7 +3606,7 @@
         <v>35520</v>
       </c>
       <c r="B148" t="n">
-        <v>12.90942680717412</v>
+        <v>12.89385345283139</v>
       </c>
       <c r="C148" t="n">
         <v>4.5</v>
@@ -3689,7 +3689,7 @@
         <v>35611</v>
       </c>
       <c r="B151" t="n">
-        <v>12.92548291215827</v>
+        <v>12.9108150904268</v>
       </c>
       <c r="C151" t="n">
         <v>4.29</v>
@@ -3772,7 +3772,7 @@
         <v>35703</v>
       </c>
       <c r="B154" t="n">
-        <v>12.92968186107083</v>
+        <v>12.91482517673959</v>
       </c>
       <c r="C154" t="n">
         <v>4.31</v>
@@ -3855,7 +3855,7 @@
         <v>35795</v>
       </c>
       <c r="B157" t="n">
-        <v>12.94444698361674</v>
+        <v>12.92930834237733</v>
       </c>
       <c r="C157" t="n">
         <v>4.37</v>
@@ -3938,7 +3938,7 @@
         <v>35885</v>
       </c>
       <c r="B160" t="n">
-        <v>12.93974497655654</v>
+        <v>12.92462438031185</v>
       </c>
       <c r="C160" t="n">
         <v>4.11</v>
@@ -4021,7 +4021,7 @@
         <v>35976</v>
       </c>
       <c r="B163" t="n">
-        <v>12.94533952297179</v>
+        <v>12.93026102418543</v>
       </c>
       <c r="C163" t="n">
         <v>4.02</v>
@@ -4104,7 +4104,7 @@
         <v>36068</v>
       </c>
       <c r="B166" t="n">
-        <v>12.94629542599585</v>
+        <v>12.93155462605107</v>
       </c>
       <c r="C166" t="n">
         <v>3.93</v>
@@ -4187,7 +4187,7 @@
         <v>36160</v>
       </c>
       <c r="B169" t="n">
-        <v>12.94300367000076</v>
+        <v>12.92796932034776</v>
       </c>
       <c r="C169" t="n">
         <v>3.37</v>
@@ -4274,7 +4274,7 @@
         <v>36250</v>
       </c>
       <c r="B172" t="n">
-        <v>12.94765016362495</v>
+        <v>12.93270392397742</v>
       </c>
       <c r="C172" t="n">
         <v>3.0466957</v>
@@ -4363,7 +4363,7 @@
         <v>36341</v>
       </c>
       <c r="B175" t="n">
-        <v>12.95170316209717</v>
+        <v>12.93645876914129</v>
       </c>
       <c r="C175" t="n">
         <v>2.6266818</v>
@@ -4452,7 +4452,7 @@
         <v>36433</v>
       </c>
       <c r="B178" t="n">
-        <v>12.96215096232647</v>
+        <v>12.94703022473174</v>
       </c>
       <c r="C178" t="n">
         <v>2.7266818</v>
@@ -4541,7 +4541,7 @@
         <v>36525</v>
       </c>
       <c r="B181" t="n">
-        <v>12.97730893442283</v>
+        <v>12.96271186235335</v>
       </c>
       <c r="C181" t="n">
         <v>3.4460455</v>
@@ -4634,7 +4634,7 @@
         <v>36616</v>
       </c>
       <c r="B184" t="n">
-        <v>12.98934293993427</v>
+        <v>12.97420298658335</v>
       </c>
       <c r="C184" t="n">
         <v>3.7470435</v>
@@ -4729,7 +4729,7 @@
         <v>36707</v>
       </c>
       <c r="B187" t="n">
-        <v>12.99575925006416</v>
+        <v>12.98066063289052</v>
       </c>
       <c r="C187" t="n">
         <v>4.5017273</v>
@@ -4824,7 +4824,7 @@
         <v>36799</v>
       </c>
       <c r="B190" t="n">
-        <v>13.00452759035661</v>
+        <v>12.98940667675559</v>
       </c>
       <c r="C190" t="n">
         <v>4.8528095</v>
@@ -4919,7 +4919,7 @@
         <v>36891</v>
       </c>
       <c r="B193" t="n">
-        <v>13.01409218539054</v>
+        <v>12.99901674359814</v>
       </c>
       <c r="C193" t="n">
         <v>4.9391579</v>
@@ -5014,7 +5014,7 @@
         <v>36981</v>
       </c>
       <c r="B196" t="n">
-        <v>13.02251519643056</v>
+        <v>13.00776992461602</v>
       </c>
       <c r="C196" t="n">
         <v>4.7086364</v>
@@ -5109,7 +5109,7 @@
         <v>37072</v>
       </c>
       <c r="B199" t="n">
-        <v>13.02170954568918</v>
+        <v>13.00652751976578</v>
       </c>
       <c r="C199" t="n">
         <v>4.4535714</v>
@@ -5204,7 +5204,7 @@
         <v>37164</v>
       </c>
       <c r="B202" t="n">
-        <v>13.01741188919448</v>
+        <v>13.00229320323953</v>
       </c>
       <c r="C202" t="n">
         <v>3.98285</v>
@@ -5299,7 +5299,7 @@
         <v>37256</v>
       </c>
       <c r="B205" t="n">
-        <v>13.01592628244291</v>
+        <v>13.00072102917222</v>
       </c>
       <c r="C205" t="n">
         <v>3.3448889</v>
@@ -5394,7 +5394,7 @@
         <v>37346</v>
       </c>
       <c r="B208" t="n">
-        <v>13.01740322603447</v>
+        <v>13.00207713634185</v>
       </c>
       <c r="C208" t="n">
         <v>3.3908</v>
@@ -5489,7 +5489,7 @@
         <v>37437</v>
       </c>
       <c r="B211" t="n">
-        <v>13.02058798306774</v>
+        <v>13.0057922570818</v>
       </c>
       <c r="C211" t="n">
         <v>3.464</v>
@@ -5584,7 +5584,7 @@
         <v>37529</v>
       </c>
       <c r="B214" t="n">
-        <v>13.0217493570717</v>
+        <v>13.00676732355892</v>
       </c>
       <c r="C214" t="n">
         <v>3.3101429</v>
@@ -5679,7 +5679,7 @@
         <v>37621</v>
       </c>
       <c r="B217" t="n">
-        <v>13.0276862571755</v>
+        <v>13.01260900063904</v>
       </c>
       <c r="C217" t="n">
         <v>2.94105</v>
@@ -5774,7 +5774,7 @@
         <v>37711</v>
       </c>
       <c r="B220" t="n">
-        <v>13.02375534565918</v>
+        <v>13.00852681915169</v>
       </c>
       <c r="C220" t="n">
         <v>2.5299524</v>
@@ -5869,7 +5869,7 @@
         <v>37802</v>
       </c>
       <c r="B223" t="n">
-        <v>13.02143325526571</v>
+        <v>13.00609873840008</v>
       </c>
       <c r="C223" t="n">
         <v>2.1518571</v>
@@ -5964,7 +5964,7 @@
         <v>37894</v>
       </c>
       <c r="B226" t="n">
-        <v>13.01914877983863</v>
+        <v>13.00406575937314</v>
       </c>
       <c r="C226" t="n">
         <v>2.1473182</v>
@@ -6059,7 +6059,7 @@
         <v>37986</v>
       </c>
       <c r="B229" t="n">
-        <v>13.02891979442372</v>
+        <v>13.01417731809956</v>
       </c>
       <c r="C229" t="n">
         <v>2.1463333</v>
@@ -6154,7 +6154,7 @@
         <v>38077</v>
       </c>
       <c r="B232" t="n">
-        <v>13.03244939191952</v>
+        <v>13.01741344411269</v>
       </c>
       <c r="C232" t="n">
         <v>2.0288261</v>
@@ -6249,7 +6249,7 @@
         <v>38168</v>
       </c>
       <c r="B235" t="n">
-        <v>13.03549177246431</v>
+        <v>13.02055587564383</v>
       </c>
       <c r="C235" t="n">
         <v>2.1126818</v>
@@ -6344,7 +6344,7 @@
         <v>38260</v>
       </c>
       <c r="B238" t="n">
-        <v>13.03647950999136</v>
+        <v>13.02170622800243</v>
       </c>
       <c r="C238" t="n">
         <v>2.1185909</v>
@@ -6439,7 +6439,7 @@
         <v>38352</v>
       </c>
       <c r="B241" t="n">
-        <v>13.03870694809692</v>
+        <v>13.02353702309743</v>
       </c>
       <c r="C241" t="n">
         <v>2.1731739</v>
@@ -6534,7 +6534,7 @@
         <v>38442</v>
       </c>
       <c r="B244" t="n">
-        <v>13.03718972893857</v>
+        <v>13.02221370612902</v>
       </c>
       <c r="C244" t="n">
         <v>2.1371905</v>
@@ -6629,7 +6629,7 @@
         <v>38533</v>
       </c>
       <c r="B247" t="n">
-        <v>13.04532832552947</v>
+        <v>13.03017681402673</v>
       </c>
       <c r="C247" t="n">
         <v>2.1110455</v>
@@ -6724,7 +6724,7 @@
         <v>38625</v>
       </c>
       <c r="B250" t="n">
-        <v>13.05072644203066</v>
+        <v>13.03551075144945</v>
       </c>
       <c r="C250" t="n">
         <v>2.1391364</v>
@@ -6819,7 +6819,7 @@
         <v>38717</v>
       </c>
       <c r="B253" t="n">
-        <v>13.05527675928995</v>
+        <v>13.04041009574612</v>
       </c>
       <c r="C253" t="n">
         <v>2.4728571</v>
@@ -6914,7 +6914,7 @@
         <v>38807</v>
       </c>
       <c r="B256" t="n">
-        <v>13.05862943916977</v>
+        <v>13.04357316836014</v>
       </c>
       <c r="C256" t="n">
         <v>2.7226087</v>
@@ -7009,7 +7009,7 @@
         <v>38898</v>
       </c>
       <c r="B259" t="n">
-        <v>13.06179137920325</v>
+        <v>13.04634545938774</v>
       </c>
       <c r="C259" t="n">
         <v>2.9856818</v>
@@ -7104,7 +7104,7 @@
         <v>38990</v>
       </c>
       <c r="B262" t="n">
-        <v>13.06478193292306</v>
+        <v>13.04959374005016</v>
       </c>
       <c r="C262" t="n">
         <v>3.335381</v>
@@ -7199,7 +7199,7 @@
         <v>39082</v>
       </c>
       <c r="B265" t="n">
-        <v>13.07843092542295</v>
+        <v>13.06366165563004</v>
       </c>
       <c r="C265" t="n">
         <v>3.6842105</v>
@@ -7294,7 +7294,7 @@
         <v>39172</v>
       </c>
       <c r="B268" t="n">
-        <v>13.07748420532524</v>
+        <v>13.06282608922636</v>
       </c>
       <c r="C268" t="n">
         <v>3.8909091</v>
@@ -7389,7 +7389,7 @@
         <v>39263</v>
       </c>
       <c r="B271" t="n">
-        <v>13.07990525348737</v>
+        <v>13.06453360884446</v>
       </c>
       <c r="C271" t="n">
         <v>4.1477619</v>
@@ -7484,7 +7484,7 @@
         <v>39355</v>
       </c>
       <c r="B274" t="n">
-        <v>13.07971262839812</v>
+        <v>13.06442213959057</v>
       </c>
       <c r="C274" t="n">
         <v>4.7417</v>
@@ -7579,7 +7579,7 @@
         <v>39447</v>
       </c>
       <c r="B277" t="n">
-        <v>13.07761158801177</v>
+        <v>13.06272737923845</v>
       </c>
       <c r="C277" t="n">
         <v>4.8483684</v>
@@ -7674,7 +7674,7 @@
         <v>39538</v>
       </c>
       <c r="B280" t="n">
-        <v>13.08849361832671</v>
+        <v>13.07344431492787</v>
       </c>
       <c r="C280" t="n">
         <v>4.5963684</v>
@@ -7769,7 +7769,7 @@
         <v>39629</v>
       </c>
       <c r="B283" t="n">
-        <v>13.07913599225019</v>
+        <v>13.06393903320079</v>
       </c>
       <c r="C283" t="n">
         <v>4.9405238</v>
@@ -7864,7 +7864,7 @@
         <v>39721</v>
       </c>
       <c r="B286" t="n">
-        <v>13.06397719840439</v>
+        <v>13.04860100706188</v>
       </c>
       <c r="C286" t="n">
         <v>5.0191818</v>
@@ -7959,7 +7959,7 @@
         <v>39813</v>
       </c>
       <c r="B289" t="n">
-        <v>13.03983423110269</v>
+        <v>13.02537372808026</v>
       </c>
       <c r="C289" t="n">
         <v>3.292619</v>
@@ -8054,7 +8054,7 @@
         <v>39903</v>
       </c>
       <c r="B292" t="n">
-        <v>13.01497747870899</v>
+        <v>13.00058888647825</v>
       </c>
       <c r="C292" t="n">
         <v>1.6354545</v>
@@ -8149,7 +8149,7 @@
         <v>39994</v>
       </c>
       <c r="B295" t="n">
-        <v>13.00959885292867</v>
+        <v>12.9943506716332</v>
       </c>
       <c r="C295" t="n">
         <v>1.2279091</v>
@@ -8244,7 +8244,7 @@
         <v>40086</v>
       </c>
       <c r="B298" t="n">
-        <v>13.01295244766103</v>
+        <v>12.9979491539401</v>
       </c>
       <c r="C298" t="n">
         <v>0.7720909</v>
@@ -8339,7 +8339,7 @@
         <v>40178</v>
       </c>
       <c r="B301" t="n">
-        <v>13.01562969716518</v>
+        <v>13.00027370649262</v>
       </c>
       <c r="C301" t="n">
         <v>0.7120455</v>
@@ -8434,7 +8434,7 @@
         <v>40268</v>
       </c>
       <c r="B304" t="n">
-        <v>13.01944920035201</v>
+        <v>13.00388767691104</v>
       </c>
       <c r="C304" t="n">
         <v>0.6449565</v>
@@ -8529,7 +8529,7 @@
         <v>40359</v>
       </c>
       <c r="B307" t="n">
-        <v>13.02618391988759</v>
+        <v>13.01063440387587</v>
       </c>
       <c r="C307" t="n">
         <v>0.7275909</v>
@@ -8624,7 +8624,7 @@
         <v>40451</v>
       </c>
       <c r="B310" t="n">
-        <v>13.02883854292217</v>
+        <v>13.01416572977996</v>
       </c>
       <c r="C310" t="n">
         <v>0.8804999999999999</v>
@@ -8719,7 +8719,7 @@
         <v>40543</v>
       </c>
       <c r="B313" t="n">
-        <v>13.03738484188258</v>
+        <v>13.02327338309302</v>
       </c>
       <c r="C313" t="n">
         <v>1.0216957</v>
@@ -8814,7 +8814,7 @@
         <v>40633</v>
       </c>
       <c r="B316" t="n">
-        <v>13.04303549751386</v>
+        <v>13.02748462452202</v>
       </c>
       <c r="C316" t="n">
         <v>1.1755217</v>
@@ -8909,7 +8909,7 @@
         <v>40724</v>
       </c>
       <c r="B319" t="n">
-        <v>13.0406492904209</v>
+        <v>13.02577009477553</v>
       </c>
       <c r="C319" t="n">
         <v>1.4885909</v>
@@ -9004,7 +9004,7 @@
         <v>40816</v>
       </c>
       <c r="B322" t="n">
-        <v>13.03606839828591</v>
+        <v>13.02146179480143</v>
       </c>
       <c r="C322" t="n">
         <v>1.5364545</v>
@@ -9099,7 +9099,7 @@
         <v>40908</v>
       </c>
       <c r="B325" t="n">
-        <v>13.02623588368997</v>
+        <v>13.0122625330092</v>
       </c>
       <c r="C325" t="n">
         <v>1.4260952</v>
@@ -9194,7 +9194,7 @@
         <v>40999</v>
       </c>
       <c r="B328" t="n">
-        <v>13.01575964482806</v>
+        <v>13.0009915848564</v>
       </c>
       <c r="C328" t="n">
         <v>0.8584545</v>
@@ -9289,7 +9289,7 @@
         <v>41090</v>
       </c>
       <c r="B331" t="n">
-        <v>13.00737622960836</v>
+        <v>12.99277255338817</v>
       </c>
       <c r="C331" t="n">
         <v>0.6588571</v>
@@ -9384,7 +9384,7 @@
         <v>41182</v>
       </c>
       <c r="B334" t="n">
-        <v>13.00072035156192</v>
+        <v>12.98662337616983</v>
       </c>
       <c r="C334" t="n">
         <v>0.2463</v>
@@ -9479,7 +9479,7 @@
         <v>41274</v>
       </c>
       <c r="B337" t="n">
-        <v>12.99301271903305</v>
+        <v>12.9807486597005</v>
       </c>
       <c r="C337" t="n">
         <v>0.1854737</v>
@@ -9574,7 +9574,7 @@
         <v>41364</v>
       </c>
       <c r="B340" t="n">
-        <v>12.98469108019913</v>
+        <v>12.97177697133319</v>
       </c>
       <c r="C340" t="n">
         <v>0.20605</v>
@@ -9669,7 +9669,7 @@
         <v>41455</v>
       </c>
       <c r="B343" t="n">
-        <v>12.98445671293629</v>
+        <v>12.97282849504131</v>
       </c>
       <c r="C343" t="n">
         <v>0.21025</v>
@@ -9764,7 +9764,7 @@
         <v>41547</v>
       </c>
       <c r="B346" t="n">
-        <v>12.98779441812221</v>
+        <v>12.97657939891305</v>
       </c>
       <c r="C346" t="n">
         <v>0.2232381</v>
@@ -9859,7 +9859,7 @@
         <v>41639</v>
       </c>
       <c r="B349" t="n">
-        <v>12.98632255307388</v>
+        <v>12.97537151200888</v>
       </c>
       <c r="C349" t="n">
         <v>0.2735</v>
@@ -9954,7 +9954,7 @@
         <v>41729</v>
       </c>
       <c r="B352" t="n">
-        <v>12.98673630466113</v>
+        <v>12.97465794891535</v>
       </c>
       <c r="C352" t="n">
         <v>0.3053333</v>
@@ -10049,7 +10049,7 @@
         <v>41820</v>
       </c>
       <c r="B355" t="n">
-        <v>12.98699670167759</v>
+        <v>12.97469875091577</v>
       </c>
       <c r="C355" t="n">
         <v>0.2414286</v>
@@ -10144,7 +10144,7 @@
         <v>41912</v>
       </c>
       <c r="B358" t="n">
-        <v>12.98707638747744</v>
+        <v>12.9750937024026</v>
       </c>
       <c r="C358" t="n">
         <v>0.09709089999999999</v>
@@ -10239,7 +10239,7 @@
         <v>42004</v>
       </c>
       <c r="B361" t="n">
-        <v>12.98546770335467</v>
+        <v>12.97440313058101</v>
       </c>
       <c r="C361" t="n">
         <v>0.0809048</v>
@@ -10334,7 +10334,7 @@
         <v>42094</v>
       </c>
       <c r="B364" t="n">
-        <v>12.98947018108921</v>
+        <v>12.97763952508964</v>
       </c>
       <c r="C364" t="n">
         <v>0.0271818</v>
@@ -10429,7 +10429,7 @@
         <v>42185</v>
       </c>
       <c r="B367" t="n">
-        <v>12.99375902694836</v>
+        <v>12.98249399925816</v>
       </c>
       <c r="C367" t="n">
         <v>-0.0139091</v>
@@ -10524,7 +10524,7 @@
         <v>42277</v>
       </c>
       <c r="B370" t="n">
-        <v>12.99408558897405</v>
+        <v>12.98423285354202</v>
       </c>
       <c r="C370" t="n">
         <v>-0.0370455</v>
@@ -10619,7 +10619,7 @@
         <v>42369</v>
       </c>
       <c r="B373" t="n">
-        <v>12.9986562539393</v>
+        <v>12.99046105712061</v>
       </c>
       <c r="C373" t="n">
         <v>-0.1263182</v>
@@ -10714,7 +10714,7 @@
         <v>42460</v>
       </c>
       <c r="B376" t="n">
-        <v>13.00071380130536</v>
+        <v>12.9918274937596</v>
       </c>
       <c r="C376" t="n">
         <v>-0.2285238</v>
@@ -10809,7 +10809,7 @@
         <v>42551</v>
       </c>
       <c r="B379" t="n">
-        <v>13.00394689116048</v>
+        <v>12.99554017731763</v>
       </c>
       <c r="C379" t="n">
         <v>-0.2679091</v>
@@ -10904,7 +10904,7 @@
         <v>42643</v>
       </c>
       <c r="B382" t="n">
-        <v>13.01076455502134</v>
+        <v>13.00320229267433</v>
       </c>
       <c r="C382" t="n">
         <v>-0.3016364</v>
@@ -10999,7 +10999,7 @@
         <v>42735</v>
       </c>
       <c r="B385" t="n">
-        <v>13.01432617149417</v>
+        <v>13.00705667310698</v>
       </c>
       <c r="C385" t="n">
         <v>-0.3157619</v>
@@ -11094,7 +11094,7 @@
         <v>42825</v>
       </c>
       <c r="B388" t="n">
-        <v>13.0191527712562</v>
+        <v>13.01172205390376</v>
       </c>
       <c r="C388" t="n">
         <v>-0.3293478</v>
@@ -11189,7 +11189,7 @@
         <v>42916</v>
       </c>
       <c r="B391" t="n">
-        <v>13.02342243434893</v>
+        <v>13.01568043216627</v>
       </c>
       <c r="C391" t="n">
         <v>-0.33</v>
@@ -11284,7 +11284,7 @@
         <v>43008</v>
       </c>
       <c r="B394" t="n">
-        <v>13.02419493666126</v>
+        <v>13.0173596869657</v>
       </c>
       <c r="C394" t="n">
         <v>-0.329381</v>
@@ -11379,7 +11379,7 @@
         <v>43100</v>
       </c>
       <c r="B397" t="n">
-        <v>13.03011935214018</v>
+        <v>13.02359861740314</v>
       </c>
       <c r="C397" t="n">
         <v>-0.3278947</v>
@@ -11474,7 +11474,7 @@
         <v>43190</v>
       </c>
       <c r="B400" t="n">
-        <v>13.02867799689843</v>
+        <v>13.02184843629845</v>
       </c>
       <c r="C400" t="n">
         <v>-0.3279048</v>
@@ -11569,7 +11569,7 @@
         <v>43281</v>
       </c>
       <c r="B403" t="n">
-        <v>13.03146423465582</v>
+        <v>13.02473401036309</v>
       </c>
       <c r="C403" t="n">
         <v>-0.3220476</v>
@@ -11664,7 +11664,7 @@
         <v>43373</v>
       </c>
       <c r="B406" t="n">
-        <v>13.03058005093476</v>
+        <v>13.02580093384494</v>
       </c>
       <c r="C406" t="n">
         <v>-0.31885</v>
@@ -11759,7 +11759,7 @@
         <v>43465</v>
       </c>
       <c r="B409" t="n">
-        <v>13.03335859672327</v>
+        <v>13.03020729819093</v>
       </c>
       <c r="C409" t="n">
         <v>-0.3118947</v>
@@ -11854,7 +11854,7 @@
         <v>43555</v>
       </c>
       <c r="B412" t="n">
-        <v>13.03560280532415</v>
+        <v>13.03149248934712</v>
       </c>
       <c r="C412" t="n">
         <v>-0.3091905</v>
@@ -11949,7 +11949,7 @@
         <v>43646</v>
       </c>
       <c r="B415" t="n">
-        <v>13.03955529961701</v>
+        <v>13.03561938284665</v>
       </c>
       <c r="C415" t="n">
         <v>-0.3289</v>
@@ -12044,7 +12044,7 @@
         <v>43738</v>
       </c>
       <c r="B418" t="n">
-        <v>13.03412346425491</v>
+        <v>13.03099342469956</v>
       </c>
       <c r="C418" t="n">
         <v>-0.4175714</v>
@@ -12139,7 +12139,7 @@
         <v>43830</v>
       </c>
       <c r="B421" t="n">
-        <v>13.03148832785357</v>
+        <v>13.02674965153456</v>
       </c>
       <c r="C421" t="n">
         <v>-0.3947</v>
@@ -12234,7 +12234,7 @@
         <v>43921</v>
       </c>
       <c r="B424" t="n">
-        <v>12.97284405625955</v>
+        <v>12.97099266322273</v>
       </c>
       <c r="C424" t="n">
         <v>-0.4166364</v>
@@ -12327,7 +12327,7 @@
         <v>44012</v>
       </c>
       <c r="B427" t="n">
-        <v>12.83946504460287</v>
+        <v>12.83622118539452</v>
       </c>
       <c r="C427" t="n">
         <v>-0.376</v>
@@ -12422,7 +12422,7 @@
         <v>44104</v>
       </c>
       <c r="B430" t="n">
-        <v>12.9720243240904</v>
+        <v>12.96860408764065</v>
       </c>
       <c r="C430" t="n">
         <v>-0.4913636</v>
@@ -12517,7 +12517,7 @@
         <v>44196</v>
       </c>
       <c r="B433" t="n">
-        <v>12.9747590235521</v>
+        <v>12.97377218163377</v>
       </c>
       <c r="C433" t="n">
         <v>-0.5380909</v>
@@ -12612,7 +12612,7 @@
         <v>44286</v>
       </c>
       <c r="B436" t="n">
-        <v>12.99112922980502</v>
+        <v>12.98965975636807</v>
       </c>
       <c r="C436" t="n">
         <v>-0.539087</v>
@@ -12707,7 +12707,7 @@
         <v>44377</v>
       </c>
       <c r="B439" t="n">
-        <v>13.01609200259578</v>
+        <v>13.01543452143241</v>
       </c>
       <c r="C439" t="n">
         <v>-0.5429091</v>
@@ -12802,7 +12802,7 @@
         <v>44469</v>
       </c>
       <c r="B442" t="n">
-        <v>13.03933974786127</v>
+        <v>13.04093182239533</v>
       </c>
       <c r="C442" t="n">
         <v>-0.5450455</v>
@@ -12897,7 +12897,7 @@
         <v>44561</v>
       </c>
       <c r="B445" t="n">
-        <v>13.05539802054833</v>
+        <v>13.05685585360195</v>
       </c>
       <c r="C445" t="n">
         <v>-0.5819565</v>
@@ -12992,7 +12992,7 @@
         <v>44651</v>
       </c>
       <c r="B448" t="n">
-        <v>13.06250678557734</v>
+        <v>13.06344020729765</v>
       </c>
       <c r="C448" t="n">
         <v>-0.4954348</v>
@@ -13087,7 +13087,7 @@
         <v>44742</v>
       </c>
       <c r="B451" t="n">
-        <v>13.07801329148243</v>
+        <v>13.07906540350873</v>
       </c>
       <c r="C451" t="n">
         <v>-0.2392273</v>
@@ -13182,7 +13182,7 @@
         <v>44834</v>
       </c>
       <c r="B454" t="n">
-        <v>13.07954084146818</v>
+        <v>13.08061178427447</v>
       </c>
       <c r="C454" t="n">
         <v>1.0108636</v>
@@ -13277,7 +13277,7 @@
         <v>44926</v>
       </c>
       <c r="B457" t="n">
-        <v>13.07716431749456</v>
+        <v>13.07820415385796</v>
       </c>
       <c r="C457" t="n">
         <v>2.0634762</v>
@@ -13372,7 +13372,7 @@
         <v>45016</v>
       </c>
       <c r="B460" t="n">
-        <v>13.08289962671982</v>
+        <v>13.08428947840824</v>
       </c>
       <c r="C460" t="n">
         <v>2.9105652</v>
@@ -13467,7 +13467,7 @@
         <v>45107</v>
       </c>
       <c r="B463" t="n">
-        <v>13.08317275979817</v>
+        <v>13.08402953486502</v>
       </c>
       <c r="C463" t="n">
         <v>3.5358636</v>
@@ -13562,7 +13562,7 @@
         <v>45199</v>
       </c>
       <c r="B466" t="n">
-        <v>13.08414860612183</v>
+        <v>13.08571951731157</v>
       </c>
       <c r="C466" t="n">
         <v>3.8800476</v>
@@ -13657,7 +13657,7 @@
         <v>45291</v>
       </c>
       <c r="B469" t="n">
-        <v>13.0876619887029</v>
+        <v>13.09101924240426</v>
       </c>
       <c r="C469" t="n">
         <v>3.9348947</v>
@@ -13752,7 +13752,7 @@
         <v>45382</v>
       </c>
       <c r="B472" t="n">
-        <v>13.08847810145827</v>
+        <v>13.09245721283948</v>
       </c>
       <c r="C472" t="n">
         <v>3.9231</v>
@@ -13847,7 +13847,7 @@
         <v>45473</v>
       </c>
       <c r="B475" t="n">
-        <v>13.09040593472351</v>
+        <v>13.09507049203304</v>
       </c>
       <c r="C475" t="n">
         <v>3.7245</v>
@@ -13942,7 +13942,7 @@
         <v>45565</v>
       </c>
       <c r="B478" t="n">
-        <v>13.0904996789291</v>
+        <v>13.09564520475158</v>
       </c>
       <c r="C478" t="n">
         <v>3.4337143</v>
@@ -14037,7 +14037,7 @@
         <v>45657</v>
       </c>
       <c r="B481" t="n">
-        <v>13.09188891207126</v>
+        <v>13.09671710522517</v>
       </c>
       <c r="C481" t="n">
         <v>2.8246</v>
@@ -14132,7 +14132,7 @@
         <v>45747</v>
       </c>
       <c r="B484" t="n">
-        <v>13.09525853773219</v>
+        <v>13.1006386961453</v>
       </c>
       <c r="C484" t="n">
         <v>2.4424286</v>
@@ -14227,7 +14227,7 @@
         <v>45838</v>
       </c>
       <c r="B487" t="n">
-        <v>13.09511303661417</v>
+        <v>13.10033226487841</v>
       </c>
       <c r="C487" t="n">
         <v>1.983619</v>
@@ -14322,7 +14322,7 @@
         <v>45930</v>
       </c>
       <c r="B490" t="n">
-        <v>13.09699018327087</v>
+        <v>13.1024779666817</v>
       </c>
       <c r="C490" t="n">
         <v>2.0272727</v>
@@ -14417,7 +14417,7 @@
         <v>46022</v>
       </c>
       <c r="B493" t="n">
-        <v>13.10035904814018</v>
+        <v>13.10565394923136</v>
       </c>
       <c r="C493" t="n">
         <v>2.0484286</v>
@@ -14512,7 +14512,7 @@
         <v>46112</v>
       </c>
       <c r="B496" t="n">
-        <v>13.10351893090627</v>
+        <v>13.10888636912838</v>
       </c>
       <c r="C496" t="n">
         <v>2.1094091</v>
@@ -14607,7 +14607,7 @@
         <v>46203</v>
       </c>
       <c r="B499" t="n">
-        <v>13.10523410550714</v>
+        <v>13.11043774893473</v>
       </c>
       <c r="C499" t="n">
         <v>2.339</v>

--- a/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
@@ -14711,7 +14711,9 @@
       <c r="I502" t="n">
         <v>4.652053771886941</v>
       </c>
-      <c r="J502" t="inlineStr"/>
+      <c r="J502" t="n">
+        <v>4.596689494135473</v>
+      </c>
       <c r="K502" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
@@ -5085,7 +5085,7 @@
         <v>4.653960350157523</v>
       </c>
       <c r="E198" t="n">
-        <v>4.789157022101107</v>
+        <v>4.788324729085938</v>
       </c>
       <c r="F198" t="n">
         <v>4.755312844417811</v>
@@ -5118,7 +5118,7 @@
         <v>4.665324108807838</v>
       </c>
       <c r="E199" t="n">
-        <v>4.791649752930709</v>
+        <v>4.79081953287472</v>
       </c>
       <c r="F199" t="n">
         <v>4.767289035464526</v>
@@ -5244,7 +5244,7 @@
         <v>4.503137460422939</v>
       </c>
       <c r="E203" t="n">
-        <v>4.766438333584214</v>
+        <v>4.767289035464526</v>
       </c>
       <c r="F203" t="n">
         <v>4.771531723203316</v>
@@ -5403,7 +5403,7 @@
         <v>4.697749367281185</v>
       </c>
       <c r="E208" t="n">
-        <v>4.777441406928545</v>
+        <v>4.776599301615622</v>
       </c>
       <c r="F208" t="n">
         <v>4.786658062033468</v>
@@ -5560,7 +5560,7 @@
         <v>4.596129441335942</v>
       </c>
       <c r="E213" t="n">
-        <v>4.752727750345706</v>
+        <v>4.753590191106364</v>
       </c>
       <c r="F213" t="n">
         <v>4.807294370078226</v>
@@ -7334,7 +7334,7 @@
         <v>4.724729421045731</v>
       </c>
       <c r="E269" t="n">
-        <v>4.798266815950004</v>
+        <v>4.799090878625398</v>
       </c>
       <c r="F269" t="n">
         <v>4.981549713201159</v>
@@ -7935,7 +7935,7 @@
         <v>4.401829261970061</v>
       </c>
       <c r="E288" t="n">
-        <v>4.687671407499835</v>
+        <v>4.686750172980514</v>
       </c>
       <c r="F288" t="n">
         <v>4.890349128221754</v>
@@ -9645,7 +9645,7 @@
         <v>4.387014176184921</v>
       </c>
       <c r="E342" t="n">
-        <v>4.554928969551344</v>
+        <v>4.553876891600541</v>
       </c>
       <c r="F342" t="n">
         <v>4.484131857611035</v>
@@ -9740,7 +9740,7 @@
         <v>4.485259889315534</v>
       </c>
       <c r="E345" t="n">
-        <v>4.533674184283021</v>
+        <v>4.534747721691546</v>
       </c>
       <c r="F345" t="n">
         <v>4.506454213048934</v>
@@ -10153,7 +10153,7 @@
         <v>4.516338972281476</v>
       </c>
       <c r="E358" t="n">
-        <v>4.533674184283021</v>
+        <v>4.534747721691546</v>
       </c>
       <c r="F358" t="n">
         <v>4.401829261970061</v>
@@ -10469,7 +10469,7 @@
         <v>4.630837932736669</v>
       </c>
       <c r="E368" t="n">
-        <v>4.5685062016165</v>
+        <v>4.56746831880408</v>
       </c>
       <c r="F368" t="n">
         <v>4.407938016458383</v>
@@ -11008,7 +11008,7 @@
         <v>4.619073091157083</v>
       </c>
       <c r="E385" t="n">
-        <v>4.607168188650764</v>
+        <v>4.606169686321175</v>
       </c>
       <c r="F385" t="n">
         <v>4.420044701861403</v>
@@ -11260,7 +11260,7 @@
         <v>4.69866052907543</v>
       </c>
       <c r="E393" t="n">
-        <v>4.637637376125593</v>
+        <v>4.636668853047462</v>
       </c>
       <c r="F393" t="n">
         <v>4.417635062141249</v>
@@ -12683,7 +12683,7 @@
         <v>4.73707525686803</v>
       </c>
       <c r="E438" t="n">
-        <v>4.58700621536042</v>
+        <v>4.585987366571318</v>
       </c>
       <c r="F438" t="n">
         <v>4.563305981889393</v>
@@ -12778,7 +12778,7 @@
         <v>4.769836807543325</v>
       </c>
       <c r="E441" t="n">
-        <v>4.600157644164547</v>
+        <v>4.601162164590552</v>
       </c>
       <c r="F441" t="n">
         <v>4.618086411254637</v>
@@ -12842,7 +12842,7 @@
         <v>4.794963757620747</v>
       </c>
       <c r="E443" t="n">
-        <v>4.606169686321175</v>
+        <v>4.607168188650764</v>
       </c>
       <c r="F443" t="n">
         <v>4.68213122712422</v>
@@ -13001,7 +13001,7 @@
         <v>4.642465970731788</v>
       </c>
       <c r="E448" t="n">
-        <v>4.620058798481842</v>
+        <v>4.619073091157083</v>
       </c>
       <c r="F448" t="n">
         <v>4.783316371371566</v>
@@ -13096,7 +13096,7 @@
         <v>4.649187071404866</v>
       </c>
       <c r="E451" t="n">
-        <v>4.596129441335942</v>
+        <v>4.59511985013459</v>
       </c>
       <c r="F451" t="n">
         <v>4.799090878625398</v>
@@ -13538,7 +13538,7 @@
         <v>4.604169685654508</v>
       </c>
       <c r="E465" t="n">
-        <v>4.58700621536042</v>
+        <v>4.588024027153121</v>
       </c>
       <c r="F465" t="n">
         <v>4.906015244966153</v>
@@ -13761,7 +13761,7 @@
         <v>4.614129927359564</v>
       </c>
       <c r="E472" t="n">
-        <v>4.55597994179732</v>
+        <v>4.554928969551344</v>
       </c>
       <c r="F472" t="n">
         <v>4.880526608749236</v>
@@ -13887,7 +13887,7 @@
         <v>4.606169686321175</v>
       </c>
       <c r="E476" t="n">
-        <v>4.535820107853298</v>
+        <v>4.534747721691546</v>
       </c>
       <c r="F476" t="n">
         <v>4.906015244966153</v>
@@ -13918,7 +13918,7 @@
         <v>4.592084946439436</v>
       </c>
       <c r="E477" t="n">
-        <v>4.543294782270004</v>
+        <v>4.545420181582317</v>
       </c>
       <c r="F477" t="n">
         <v>4.903050083416319</v>
@@ -13951,7 +13951,7 @@
         <v>4.603168183317418</v>
       </c>
       <c r="E478" t="n">
-        <v>4.532599493153256</v>
+        <v>4.533674184283021</v>
       </c>
       <c r="F478" t="n">
         <v>4.903050083416319</v>
@@ -14172,7 +14172,7 @@
         <v>4.566429357671661</v>
       </c>
       <c r="E485" t="n">
-        <v>4.541164856012179</v>
+        <v>4.540098189244376</v>
       </c>
       <c r="F485" t="n">
         <v>4.932313327320786</v>
@@ -14203,7 +14203,7 @@
         <v>4.596129441335942</v>
       </c>
       <c r="E486" t="n">
-        <v>4.536891345234797</v>
+        <v>4.535820107853298</v>
       </c>
       <c r="F486" t="n">
         <v>4.934473933130691</v>
@@ -14236,7 +14236,7 @@
         <v>4.598145571051127</v>
       </c>
       <c r="E487" t="n">
-        <v>4.543294782270004</v>
+        <v>4.542230386214217</v>
       </c>
       <c r="F487" t="n">
         <v>4.93662988078576</v>
@@ -14267,7 +14267,7 @@
         <v>4.601162164590552</v>
       </c>
       <c r="E488" t="n">
-        <v>4.546481189639412</v>
+        <v>4.545420181582317</v>
       </c>
       <c r="F488" t="n">
         <v>4.940927881671436</v>
@@ -14298,7 +14298,7 @@
         <v>4.589040804058207</v>
       </c>
       <c r="E489" t="n">
-        <v>4.525044141508807</v>
+        <v>4.528289141652134</v>
       </c>
       <c r="F489" t="n">
         <v>4.926528784799256</v>
@@ -14457,7 +14457,7 @@
         <v>4.629862798578463</v>
       </c>
       <c r="E494" t="n">
-        <v>4.539030383483547</v>
+        <v>4.537961436294641</v>
       </c>
       <c r="F494" t="n">
         <v>4.93806460126142</v>
@@ -14488,7 +14488,7 @@
         <v>4.623991940228679</v>
       </c>
       <c r="E495" t="n">
-        <v>4.540098189244376</v>
+        <v>4.539030383483547</v>
       </c>
       <c r="F495" t="n">
         <v>4.93806460126142</v>
@@ -14552,7 +14552,7 @@
         <v>4.583946549536464</v>
       </c>
       <c r="E497" t="n">
-        <v>4.550714000192032</v>
+        <v>4.549657476057832</v>
       </c>
       <c r="F497" t="n">
         <v>4.963543686562405</v>
@@ -14583,7 +14583,7 @@
         <v>4.585987366571318</v>
       </c>
       <c r="E498" t="n">
-        <v>4.548599834499697</v>
+        <v>4.546481189639412</v>
       </c>
       <c r="F498" t="n">
         <v>4.964242254526545</v>
@@ -14616,7 +14616,7 @@
         <v>4.598145571051127</v>
       </c>
       <c r="E499" t="n">
-        <v>4.537961436294641</v>
+        <v>4.536891345234797</v>
       </c>
       <c r="F499" t="n">
         <v>4.94306997460049</v>
@@ -14647,7 +14647,7 @@
         <v>4.601162164590552</v>
       </c>
       <c r="E500" t="n">
-        <v>4.545420181582317</v>
+        <v>4.543294782270004</v>
       </c>
       <c r="F500" t="n">
         <v>4.92870191133357</v>
@@ -14677,7 +14677,9 @@
       <c r="D501" t="n">
         <v>4.611152257665639</v>
       </c>
-      <c r="E501" t="inlineStr"/>
+      <c r="E501" t="n">
+        <v>4.530446639792155</v>
+      </c>
       <c r="F501" t="inlineStr"/>
       <c r="G501" t="n">
         <v>4.580877493419047</v>

--- a/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,24 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,64 +421,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>GDPyoy</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>EURIBOR 3M</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EcSent</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>IPall</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CONSindex</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>retail</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>unemployment</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>HICP</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Brent</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>STOXX</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>31078</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -511,7 +497,7 @@
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>31106</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -530,7 +516,7 @@
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>31137</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -549,7 +535,7 @@
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>31167</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -568,7 +554,7 @@
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>31198</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -587,7 +573,7 @@
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>31228</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -606,7 +592,7 @@
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>31259</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -625,7 +611,7 @@
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>31290</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -644,7 +630,7 @@
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>31320</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -663,7 +649,7 @@
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>31351</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -682,7 +668,7 @@
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>31381</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -701,7 +687,7 @@
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>31412</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -720,7 +706,7 @@
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>31443</v>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -739,7 +725,7 @@
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>31471</v>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -758,7 +744,7 @@
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>31502</v>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -777,7 +763,7 @@
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>31532</v>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -796,7 +782,7 @@
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>31563</v>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -815,7 +801,7 @@
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>31593</v>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -834,7 +820,7 @@
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>31624</v>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -853,7 +839,7 @@
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>31655</v>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -872,7 +858,7 @@
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>31685</v>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -891,7 +877,7 @@
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>31716</v>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -910,7 +896,7 @@
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>31746</v>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -929,7 +915,7 @@
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>31777</v>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -948,7 +934,7 @@
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>31808</v>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -967,7 +953,7 @@
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>31836</v>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -986,7 +972,7 @@
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>31867</v>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1005,7 +991,7 @@
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>31897</v>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1024,7 +1010,7 @@
       <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>31928</v>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1043,7 +1029,7 @@
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>31958</v>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1062,7 +1048,7 @@
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>31989</v>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1081,7 +1067,7 @@
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>32020</v>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1100,7 +1086,7 @@
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>32050</v>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1119,7 +1105,7 @@
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>32081</v>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1138,7 +1124,7 @@
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>32111</v>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1157,7 +1143,7 @@
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>32142</v>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1176,7 +1162,7 @@
       <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>32173</v>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1195,7 +1181,7 @@
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>32202</v>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1214,7 +1200,7 @@
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>32233</v>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1233,7 +1219,7 @@
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>32263</v>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1252,7 +1238,7 @@
       <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>32294</v>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1271,7 +1257,7 @@
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>32324</v>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1290,7 +1276,7 @@
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>32355</v>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1309,7 +1295,7 @@
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>32386</v>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1328,7 +1314,7 @@
       <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>32416</v>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1347,7 +1333,7 @@
       <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>32447</v>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1366,7 +1352,7 @@
       <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>32477</v>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1385,7 +1371,7 @@
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>32508</v>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1404,7 +1390,7 @@
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>32539</v>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1423,7 +1409,7 @@
       <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>32567</v>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1442,7 +1428,7 @@
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>32598</v>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1461,7 +1447,7 @@
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>32628</v>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1480,7 +1466,7 @@
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>32659</v>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1499,7 +1485,7 @@
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>32689</v>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -1518,7 +1504,7 @@
       <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>32720</v>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1537,7 +1523,7 @@
       <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>32751</v>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1556,7 +1542,7 @@
       <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>32781</v>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -1575,7 +1561,7 @@
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>32812</v>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -1594,7 +1580,7 @@
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>32842</v>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -1613,7 +1599,7 @@
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>32873</v>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -1632,7 +1618,7 @@
       <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>32904</v>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -1653,7 +1639,7 @@
       <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>32932</v>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -1674,7 +1660,7 @@
       <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>32963</v>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -1695,7 +1681,7 @@
       <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>32993</v>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -1716,7 +1702,7 @@
       <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>33024</v>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -1737,7 +1723,7 @@
       <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>33054</v>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -1758,7 +1744,7 @@
       <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>33085</v>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -1779,7 +1765,7 @@
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>33116</v>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -1800,7 +1786,7 @@
       <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>33146</v>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -1821,7 +1807,7 @@
       <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>33177</v>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -1842,7 +1828,7 @@
       <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>33207</v>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1863,7 +1849,7 @@
       <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>33238</v>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -1884,7 +1870,7 @@
       <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>33269</v>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1905,7 +1891,7 @@
       <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>33297</v>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -1926,7 +1912,7 @@
       <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>33328</v>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -1947,7 +1933,7 @@
       <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>33358</v>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -1968,7 +1954,7 @@
       <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>33389</v>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -1989,7 +1975,7 @@
       <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>33419</v>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -2010,7 +1996,7 @@
       <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>33450</v>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2031,7 +2017,7 @@
       <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>33481</v>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2052,7 +2038,7 @@
       <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>33511</v>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -2073,7 +2059,7 @@
       <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>33542</v>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2094,7 +2080,7 @@
       <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>33572</v>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2115,7 +2101,7 @@
       <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>33603</v>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -2136,7 +2122,7 @@
       <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>33634</v>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -2157,7 +2143,7 @@
       <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>33663</v>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -2178,7 +2164,7 @@
       <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>33694</v>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -2199,7 +2185,7 @@
       <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>33724</v>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -2220,7 +2206,7 @@
       <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>33755</v>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -2241,7 +2227,7 @@
       <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>33785</v>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -2262,7 +2248,7 @@
       <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>33816</v>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -2283,7 +2269,7 @@
       <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>33847</v>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -2304,7 +2290,7 @@
       <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>33877</v>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -2325,7 +2311,7 @@
       <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>33908</v>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -2346,7 +2332,7 @@
       <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>33938</v>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -2367,7 +2353,7 @@
       <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>33969</v>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -2388,7 +2374,7 @@
       <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>34000</v>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -2409,7 +2395,7 @@
       <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>34028</v>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -2430,7 +2416,7 @@
       <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>34059</v>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -2451,7 +2437,7 @@
       <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>34089</v>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -2472,7 +2458,7 @@
       <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>34120</v>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -2493,7 +2479,7 @@
       <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>34150</v>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -2514,7 +2500,7 @@
       <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>34181</v>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -2535,7 +2521,7 @@
       <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>34212</v>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -2556,7 +2542,7 @@
       <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>34242</v>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -2577,7 +2563,7 @@
       <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>34273</v>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -2598,7 +2584,7 @@
       <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>34303</v>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -2619,7 +2605,7 @@
       <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>34334</v>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -2640,7 +2626,7 @@
       <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>34365</v>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -2663,7 +2649,7 @@
       <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>34393</v>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -2686,7 +2672,7 @@
       <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>34424</v>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -2709,7 +2695,7 @@
       <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>34454</v>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -2732,7 +2718,7 @@
       <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>34485</v>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -2755,7 +2741,7 @@
       <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>34515</v>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -2778,7 +2764,7 @@
       <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>34546</v>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -2801,7 +2787,7 @@
       <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>34577</v>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -2824,7 +2810,7 @@
       <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>34607</v>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -2847,7 +2833,7 @@
       <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>34638</v>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -2870,7 +2856,7 @@
       <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>34668</v>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -2893,7 +2879,7 @@
       <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>34699</v>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -2916,7 +2902,7 @@
       <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>34730</v>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -2941,7 +2927,7 @@
       <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>34758</v>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -2966,7 +2952,7 @@
       <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>34789</v>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -2991,7 +2977,7 @@
       <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>34819</v>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -3016,7 +3002,7 @@
       <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>34850</v>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -3041,7 +3027,7 @@
       <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>34880</v>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -3066,7 +3052,7 @@
       <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>34911</v>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -3091,7 +3077,7 @@
       <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>34942</v>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -3116,7 +3102,7 @@
       <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>34972</v>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -3141,7 +3127,7 @@
       <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>35003</v>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -3166,7 +3152,7 @@
       <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>35033</v>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -3191,7 +3177,7 @@
       <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>35064</v>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -3216,7 +3202,7 @@
       <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>35095</v>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -3243,7 +3229,7 @@
       <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>35124</v>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -3270,7 +3256,7 @@
       <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>35155</v>
       </c>
       <c r="B136" t="n">
@@ -3299,7 +3285,7 @@
       <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>35185</v>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -3326,7 +3312,7 @@
       <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>35216</v>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -3353,7 +3339,7 @@
       <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>35246</v>
       </c>
       <c r="B139" t="n">
@@ -3382,7 +3368,7 @@
       <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>35277</v>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -3409,7 +3395,7 @@
       <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>35308</v>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -3436,7 +3422,7 @@
       <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>35338</v>
       </c>
       <c r="B142" t="n">
@@ -3465,7 +3451,7 @@
       <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>35369</v>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -3492,7 +3478,7 @@
       <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>35399</v>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -3519,7 +3505,7 @@
       <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>35430</v>
       </c>
       <c r="B145" t="n">
@@ -3548,7 +3534,7 @@
       <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>35461</v>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -3575,7 +3561,7 @@
       <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>35489</v>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -3602,7 +3588,7 @@
       <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>35520</v>
       </c>
       <c r="B148" t="n">
@@ -3631,7 +3617,7 @@
       <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>35550</v>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -3658,7 +3644,7 @@
       <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>35581</v>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -3685,7 +3671,7 @@
       <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>35611</v>
       </c>
       <c r="B151" t="n">
@@ -3714,7 +3700,7 @@
       <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>35642</v>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -3741,7 +3727,7 @@
       <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>35673</v>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -3768,7 +3754,7 @@
       <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>35703</v>
       </c>
       <c r="B154" t="n">
@@ -3797,7 +3783,7 @@
       <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>35734</v>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -3824,7 +3810,7 @@
       <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>35764</v>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -3851,7 +3837,7 @@
       <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>35795</v>
       </c>
       <c r="B157" t="n">
@@ -3880,7 +3866,7 @@
       <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>35826</v>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -3907,7 +3893,7 @@
       <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>35854</v>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -3934,7 +3920,7 @@
       <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>35885</v>
       </c>
       <c r="B160" t="n">
@@ -3963,7 +3949,7 @@
       <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>35915</v>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -3990,7 +3976,7 @@
       <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>35946</v>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -4017,7 +4003,7 @@
       <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>35976</v>
       </c>
       <c r="B163" t="n">
@@ -4046,7 +4032,7 @@
       <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>36007</v>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -4073,7 +4059,7 @@
       <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>36038</v>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -4100,7 +4086,7 @@
       <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>36068</v>
       </c>
       <c r="B166" t="n">
@@ -4129,7 +4115,7 @@
       <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>36099</v>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -4156,7 +4142,7 @@
       <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>36129</v>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -4183,7 +4169,7 @@
       <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>36160</v>
       </c>
       <c r="B169" t="n">
@@ -4212,7 +4198,7 @@
       <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>36191</v>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -4241,7 +4227,7 @@
       <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>36219</v>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -4270,7 +4256,7 @@
       <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>36250</v>
       </c>
       <c r="B172" t="n">
@@ -4301,7 +4287,7 @@
       <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>36280</v>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -4330,7 +4316,7 @@
       <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>36311</v>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -4359,7 +4345,7 @@
       <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>36341</v>
       </c>
       <c r="B175" t="n">
@@ -4390,7 +4376,7 @@
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>36372</v>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -4419,7 +4405,7 @@
       <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>36403</v>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -4448,7 +4434,7 @@
       <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>36433</v>
       </c>
       <c r="B178" t="n">
@@ -4479,7 +4465,7 @@
       <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>36464</v>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -4508,7 +4494,7 @@
       <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>36494</v>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -4537,7 +4523,7 @@
       <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>36525</v>
       </c>
       <c r="B181" t="n">
@@ -4568,7 +4554,7 @@
       <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>36556</v>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -4599,7 +4585,7 @@
       <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>36585</v>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -4630,7 +4616,7 @@
       <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>36616</v>
       </c>
       <c r="B184" t="n">
@@ -4663,7 +4649,7 @@
       <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>36646</v>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -4694,7 +4680,7 @@
       <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>36677</v>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -4725,7 +4711,7 @@
       <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>36707</v>
       </c>
       <c r="B187" t="n">
@@ -4758,7 +4744,7 @@
       <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>36738</v>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -4789,7 +4775,7 @@
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>36769</v>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -4820,7 +4806,7 @@
       <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>36799</v>
       </c>
       <c r="B190" t="n">
@@ -4853,7 +4839,7 @@
       <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>36830</v>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -4884,7 +4870,7 @@
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>36860</v>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -4915,7 +4901,7 @@
       <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>36891</v>
       </c>
       <c r="B193" t="n">
@@ -4948,7 +4934,7 @@
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>36922</v>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -4979,7 +4965,7 @@
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>36950</v>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -5010,7 +4996,7 @@
       <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>36981</v>
       </c>
       <c r="B196" t="n">
@@ -5043,7 +5029,7 @@
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>37011</v>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -5074,7 +5060,7 @@
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>37042</v>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -5105,7 +5091,7 @@
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>37072</v>
       </c>
       <c r="B199" t="n">
@@ -5138,7 +5124,7 @@
       <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>37103</v>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -5169,7 +5155,7 @@
       <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>37134</v>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -5200,7 +5186,7 @@
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>37164</v>
       </c>
       <c r="B202" t="n">
@@ -5233,7 +5219,7 @@
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>37195</v>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -5264,7 +5250,7 @@
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>37225</v>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -5295,7 +5281,7 @@
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>37256</v>
       </c>
       <c r="B205" t="n">
@@ -5328,7 +5314,7 @@
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>37287</v>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -5359,7 +5345,7 @@
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>37315</v>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -5390,7 +5376,7 @@
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>37346</v>
       </c>
       <c r="B208" t="n">
@@ -5423,7 +5409,7 @@
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>37376</v>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -5454,7 +5440,7 @@
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>37407</v>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -5485,7 +5471,7 @@
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>37437</v>
       </c>
       <c r="B211" t="n">
@@ -5518,7 +5504,7 @@
       <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>37468</v>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -5549,7 +5535,7 @@
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>37499</v>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -5580,7 +5566,7 @@
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>37529</v>
       </c>
       <c r="B214" t="n">
@@ -5613,7 +5599,7 @@
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>37560</v>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -5644,7 +5630,7 @@
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>37590</v>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -5675,7 +5661,7 @@
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>37621</v>
       </c>
       <c r="B217" t="n">
@@ -5708,7 +5694,7 @@
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>37652</v>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -5739,7 +5725,7 @@
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>37680</v>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -5770,7 +5756,7 @@
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>37711</v>
       </c>
       <c r="B220" t="n">
@@ -5803,7 +5789,7 @@
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>37741</v>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -5834,7 +5820,7 @@
       <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>37772</v>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -5865,7 +5851,7 @@
       <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>37802</v>
       </c>
       <c r="B223" t="n">
@@ -5898,7 +5884,7 @@
       <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>37833</v>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -5929,7 +5915,7 @@
       <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>37864</v>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -5960,7 +5946,7 @@
       <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>37894</v>
       </c>
       <c r="B226" t="n">
@@ -5993,7 +5979,7 @@
       <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>37925</v>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -6024,7 +6010,7 @@
       <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>37955</v>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -6055,7 +6041,7 @@
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>37986</v>
       </c>
       <c r="B229" t="n">
@@ -6088,7 +6074,7 @@
       <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>38017</v>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -6119,7 +6105,7 @@
       <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>38046</v>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -6150,7 +6136,7 @@
       <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>38077</v>
       </c>
       <c r="B232" t="n">
@@ -6183,7 +6169,7 @@
       <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>38107</v>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -6214,7 +6200,7 @@
       <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>38138</v>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -6245,7 +6231,7 @@
       <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>38168</v>
       </c>
       <c r="B235" t="n">
@@ -6278,7 +6264,7 @@
       <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>38199</v>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -6309,7 +6295,7 @@
       <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>38230</v>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -6340,7 +6326,7 @@
       <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>38260</v>
       </c>
       <c r="B238" t="n">
@@ -6373,7 +6359,7 @@
       <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>38291</v>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -6404,7 +6390,7 @@
       <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>38321</v>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -6435,7 +6421,7 @@
       <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>38352</v>
       </c>
       <c r="B241" t="n">
@@ -6468,7 +6454,7 @@
       <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>38383</v>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -6499,7 +6485,7 @@
       <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>38411</v>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -6530,7 +6516,7 @@
       <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>38442</v>
       </c>
       <c r="B244" t="n">
@@ -6563,7 +6549,7 @@
       <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>38472</v>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -6594,7 +6580,7 @@
       <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>38503</v>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -6625,7 +6611,7 @@
       <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>38533</v>
       </c>
       <c r="B247" t="n">
@@ -6658,7 +6644,7 @@
       <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>38564</v>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -6689,7 +6675,7 @@
       <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>38595</v>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -6720,7 +6706,7 @@
       <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>38625</v>
       </c>
       <c r="B250" t="n">
@@ -6753,7 +6739,7 @@
       <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>38656</v>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -6784,7 +6770,7 @@
       <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>38686</v>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -6815,7 +6801,7 @@
       <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>38717</v>
       </c>
       <c r="B253" t="n">
@@ -6848,7 +6834,7 @@
       <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>38748</v>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -6879,7 +6865,7 @@
       <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>38776</v>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -6910,7 +6896,7 @@
       <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>38807</v>
       </c>
       <c r="B256" t="n">
@@ -6943,7 +6929,7 @@
       <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>38837</v>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -6974,7 +6960,7 @@
       <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>38868</v>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -7005,7 +6991,7 @@
       <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>38898</v>
       </c>
       <c r="B259" t="n">
@@ -7038,7 +7024,7 @@
       <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>38929</v>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -7069,7 +7055,7 @@
       <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>38960</v>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -7100,7 +7086,7 @@
       <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>38990</v>
       </c>
       <c r="B262" t="n">
@@ -7133,7 +7119,7 @@
       <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>39021</v>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -7164,7 +7150,7 @@
       <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>39051</v>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -7195,7 +7181,7 @@
       <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>39082</v>
       </c>
       <c r="B265" t="n">
@@ -7228,7 +7214,7 @@
       <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>39113</v>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -7259,7 +7245,7 @@
       <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>39141</v>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -7290,7 +7276,7 @@
       <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>39172</v>
       </c>
       <c r="B268" t="n">
@@ -7323,7 +7309,7 @@
       <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>39202</v>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -7354,7 +7340,7 @@
       <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>39233</v>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -7385,7 +7371,7 @@
       <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>39263</v>
       </c>
       <c r="B271" t="n">
@@ -7418,7 +7404,7 @@
       <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>39294</v>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -7449,7 +7435,7 @@
       <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>39325</v>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -7480,7 +7466,7 @@
       <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>39355</v>
       </c>
       <c r="B274" t="n">
@@ -7513,7 +7499,7 @@
       <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>39386</v>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -7544,7 +7530,7 @@
       <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>39416</v>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -7575,7 +7561,7 @@
       <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>39447</v>
       </c>
       <c r="B277" t="n">
@@ -7608,7 +7594,7 @@
       <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>39478</v>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -7639,7 +7625,7 @@
       <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>39507</v>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -7670,7 +7656,7 @@
       <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>39538</v>
       </c>
       <c r="B280" t="n">
@@ -7703,7 +7689,7 @@
       <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>39568</v>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -7734,7 +7720,7 @@
       <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>39599</v>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -7765,7 +7751,7 @@
       <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>39629</v>
       </c>
       <c r="B283" t="n">
@@ -7798,7 +7784,7 @@
       <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>39660</v>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -7829,7 +7815,7 @@
       <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>39691</v>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -7860,7 +7846,7 @@
       <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>39721</v>
       </c>
       <c r="B286" t="n">
@@ -7893,7 +7879,7 @@
       <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>39752</v>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -7924,7 +7910,7 @@
       <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>39782</v>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -7955,7 +7941,7 @@
       <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="B289" t="n">
@@ -7988,7 +7974,7 @@
       <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>39844</v>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -8019,7 +8005,7 @@
       <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>39872</v>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -8050,7 +8036,7 @@
       <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="B292" t="n">
@@ -8083,7 +8069,7 @@
       <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>39933</v>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -8114,7 +8100,7 @@
       <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>39964</v>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -8145,7 +8131,7 @@
       <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="B295" t="n">
@@ -8178,7 +8164,7 @@
       <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>40025</v>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -8209,7 +8195,7 @@
       <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>40056</v>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -8240,7 +8226,7 @@
       <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="B298" t="n">
@@ -8273,7 +8259,7 @@
       <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>40117</v>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -8304,7 +8290,7 @@
       <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>40147</v>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -8335,7 +8321,7 @@
       <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="B301" t="n">
@@ -8368,7 +8354,7 @@
       <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>40209</v>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -8399,7 +8385,7 @@
       <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>40237</v>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -8430,7 +8416,7 @@
       <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="B304" t="n">
@@ -8463,7 +8449,7 @@
       <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>40298</v>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -8494,7 +8480,7 @@
       <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>40329</v>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -8525,7 +8511,7 @@
       <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="B307" t="n">
@@ -8558,7 +8544,7 @@
       <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>40390</v>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -8589,7 +8575,7 @@
       <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>40421</v>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -8620,7 +8606,7 @@
       <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="B310" t="n">
@@ -8653,7 +8639,7 @@
       <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>40482</v>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -8684,7 +8670,7 @@
       <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>40512</v>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -8715,7 +8701,7 @@
       <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="B313" t="n">
@@ -8748,7 +8734,7 @@
       <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>40574</v>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -8779,7 +8765,7 @@
       <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>40602</v>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -8810,7 +8796,7 @@
       <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="B316" t="n">
@@ -8843,7 +8829,7 @@
       <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>40663</v>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -8874,7 +8860,7 @@
       <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>40694</v>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -8905,7 +8891,7 @@
       <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="B319" t="n">
@@ -8938,7 +8924,7 @@
       <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>40755</v>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -8969,7 +8955,7 @@
       <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>40786</v>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -9000,7 +8986,7 @@
       <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="B322" t="n">
@@ -9033,7 +9019,7 @@
       <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>40847</v>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -9064,7 +9050,7 @@
       <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>40877</v>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -9095,7 +9081,7 @@
       <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="B325" t="n">
@@ -9128,7 +9114,7 @@
       <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>40939</v>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -9159,7 +9145,7 @@
       <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>40968</v>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -9190,7 +9176,7 @@
       <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="B328" t="n">
@@ -9223,7 +9209,7 @@
       <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>41029</v>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -9254,7 +9240,7 @@
       <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>41060</v>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -9285,7 +9271,7 @@
       <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="B331" t="n">
@@ -9318,7 +9304,7 @@
       <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>41121</v>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -9349,7 +9335,7 @@
       <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>41152</v>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -9380,7 +9366,7 @@
       <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="B334" t="n">
@@ -9413,7 +9399,7 @@
       <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>41213</v>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -9444,7 +9430,7 @@
       <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>41243</v>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -9475,7 +9461,7 @@
       <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="B337" t="n">
@@ -9508,7 +9494,7 @@
       <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>41305</v>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -9539,7 +9525,7 @@
       <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>41333</v>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -9570,7 +9556,7 @@
       <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="B340" t="n">
@@ -9603,7 +9589,7 @@
       <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>41394</v>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -9634,7 +9620,7 @@
       <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>41425</v>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -9665,7 +9651,7 @@
       <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="B343" t="n">
@@ -9698,7 +9684,7 @@
       <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>41486</v>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -9729,7 +9715,7 @@
       <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>41517</v>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -9760,7 +9746,7 @@
       <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="B346" t="n">
@@ -9793,7 +9779,7 @@
       <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>41578</v>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -9824,7 +9810,7 @@
       <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>41608</v>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -9855,7 +9841,7 @@
       <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="B349" t="n">
@@ -9888,7 +9874,7 @@
       <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>41670</v>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -9919,7 +9905,7 @@
       <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>41698</v>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -9950,7 +9936,7 @@
       <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="B352" t="n">
@@ -9983,7 +9969,7 @@
       <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>41759</v>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -10014,7 +10000,7 @@
       <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>41790</v>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -10045,7 +10031,7 @@
       <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="B355" t="n">
@@ -10078,7 +10064,7 @@
       <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>41851</v>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -10109,7 +10095,7 @@
       <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>41882</v>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -10140,7 +10126,7 @@
       <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="B358" t="n">
@@ -10173,7 +10159,7 @@
       <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>41943</v>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -10204,7 +10190,7 @@
       <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>41973</v>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -10235,7 +10221,7 @@
       <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="B361" t="n">
@@ -10268,7 +10254,7 @@
       <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="1" t="n">
         <v>42035</v>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -10299,7 +10285,7 @@
       <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="1" t="n">
         <v>42063</v>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -10330,7 +10316,7 @@
       <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="B364" t="n">
@@ -10363,7 +10349,7 @@
       <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="1" t="n">
         <v>42124</v>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -10394,7 +10380,7 @@
       <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="1" t="n">
         <v>42155</v>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -10425,7 +10411,7 @@
       <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="B367" t="n">
@@ -10458,7 +10444,7 @@
       <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="1" t="n">
         <v>42216</v>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -10489,7 +10475,7 @@
       <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="1" t="n">
         <v>42247</v>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -10520,7 +10506,7 @@
       <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="B370" t="n">
@@ -10553,7 +10539,7 @@
       <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="1" t="n">
         <v>42308</v>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -10584,7 +10570,7 @@
       <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="1" t="n">
         <v>42338</v>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -10615,7 +10601,7 @@
       <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="B373" t="n">
@@ -10648,7 +10634,7 @@
       <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="1" t="n">
         <v>42400</v>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -10679,7 +10665,7 @@
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="1" t="n">
         <v>42429</v>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -10710,7 +10696,7 @@
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="B376" t="n">
@@ -10743,7 +10729,7 @@
       <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="1" t="n">
         <v>42490</v>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -10774,7 +10760,7 @@
       <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="1" t="n">
         <v>42521</v>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -10805,7 +10791,7 @@
       <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="B379" t="n">
@@ -10838,7 +10824,7 @@
       <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="1" t="n">
         <v>42582</v>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -10869,7 +10855,7 @@
       <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="1" t="n">
         <v>42613</v>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -10900,7 +10886,7 @@
       <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B382" t="n">
@@ -10933,7 +10919,7 @@
       <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="1" t="n">
         <v>42674</v>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -10964,7 +10950,7 @@
       <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="1" t="n">
         <v>42704</v>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -10995,7 +10981,7 @@
       <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="B385" t="n">
@@ -11028,7 +11014,7 @@
       <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="1" t="n">
         <v>42766</v>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -11059,7 +11045,7 @@
       <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="1" t="n">
         <v>42794</v>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -11090,7 +11076,7 @@
       <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B388" t="n">
@@ -11123,7 +11109,7 @@
       <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="1" t="n">
         <v>42855</v>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -11154,7 +11140,7 @@
       <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="1" t="n">
         <v>42886</v>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -11185,7 +11171,7 @@
       <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B391" t="n">
@@ -11218,7 +11204,7 @@
       <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="1" t="n">
         <v>42947</v>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -11249,7 +11235,7 @@
       <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="1" t="n">
         <v>42978</v>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -11280,7 +11266,7 @@
       <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="B394" t="n">
@@ -11313,7 +11299,7 @@
       <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="1" t="n">
         <v>43039</v>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -11344,7 +11330,7 @@
       <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="1" t="n">
         <v>43069</v>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -11375,7 +11361,7 @@
       <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="B397" t="n">
@@ -11408,7 +11394,7 @@
       <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="1" t="n">
         <v>43131</v>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -11439,7 +11425,7 @@
       <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" s="1" t="n">
         <v>43159</v>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -11470,7 +11456,7 @@
       <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="B400" t="n">
@@ -11503,7 +11489,7 @@
       <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="n">
+      <c r="A401" s="1" t="n">
         <v>43220</v>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -11534,7 +11520,7 @@
       <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="1" t="n">
         <v>43251</v>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -11565,7 +11551,7 @@
       <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="n">
+      <c r="A403" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="B403" t="n">
@@ -11598,7 +11584,7 @@
       <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="1" t="n">
         <v>43312</v>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -11629,7 +11615,7 @@
       <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="n">
+      <c r="A405" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -11660,7 +11646,7 @@
       <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="B406" t="n">
@@ -11693,7 +11679,7 @@
       <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="1" t="n">
         <v>43404</v>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -11724,7 +11710,7 @@
       <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -11755,7 +11741,7 @@
       <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="B409" t="n">
@@ -11788,7 +11774,7 @@
       <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="1" t="n">
         <v>43496</v>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -11819,7 +11805,7 @@
       <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" s="1" t="n">
         <v>43524</v>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -11850,7 +11836,7 @@
       <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="B412" t="n">
@@ -11883,7 +11869,7 @@
       <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" s="1" t="n">
         <v>43585</v>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -11914,7 +11900,7 @@
       <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -11945,7 +11931,7 @@
       <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="n">
+      <c r="A415" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="B415" t="n">
@@ -11978,7 +11964,7 @@
       <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="1" t="n">
         <v>43677</v>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -12009,7 +11995,7 @@
       <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="n">
+      <c r="A417" s="1" t="n">
         <v>43708</v>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -12040,7 +12026,7 @@
       <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="B418" t="n">
@@ -12073,7 +12059,7 @@
       <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="n">
+      <c r="A419" s="1" t="n">
         <v>43769</v>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -12104,7 +12090,7 @@
       <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="1" t="n">
         <v>43799</v>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -12135,7 +12121,7 @@
       <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="B421" t="n">
@@ -12168,7 +12154,7 @@
       <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -12199,7 +12185,7 @@
       <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="1" t="n">
         <v>43890</v>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -12230,7 +12216,7 @@
       <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="B424" t="n">
@@ -12263,7 +12249,7 @@
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="n">
+      <c r="A425" s="1" t="n">
         <v>43951</v>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -12292,7 +12278,7 @@
       <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="1" t="n">
         <v>43982</v>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -12323,7 +12309,7 @@
       <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="n">
+      <c r="A427" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="B427" t="n">
@@ -12356,7 +12342,7 @@
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -12387,7 +12373,7 @@
       <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" s="1" t="n">
         <v>44074</v>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -12418,7 +12404,7 @@
       <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="B430" t="n">
@@ -12451,7 +12437,7 @@
       <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="n">
+      <c r="A431" s="1" t="n">
         <v>44135</v>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -12482,7 +12468,7 @@
       <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="1" t="n">
         <v>44165</v>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -12513,7 +12499,7 @@
       <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="n">
+      <c r="A433" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="B433" t="n">
@@ -12546,7 +12532,7 @@
       <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="1" t="n">
         <v>44227</v>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -12577,7 +12563,7 @@
       <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="n">
+      <c r="A435" s="1" t="n">
         <v>44255</v>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -12608,7 +12594,7 @@
       <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="B436" t="n">
@@ -12641,7 +12627,7 @@
       <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
+      <c r="A437" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -12672,7 +12658,7 @@
       <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="1" t="n">
         <v>44347</v>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -12703,7 +12689,7 @@
       <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="B439" t="n">
@@ -12736,7 +12722,7 @@
       <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -12767,7 +12753,7 @@
       <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -12798,7 +12784,7 @@
       <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="B442" t="n">
@@ -12831,7 +12817,7 @@
       <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -12862,7 +12848,7 @@
       <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -12893,7 +12879,7 @@
       <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B445" t="n">
@@ -12926,7 +12912,7 @@
       <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="1" t="n">
         <v>44592</v>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -12957,7 +12943,7 @@
       <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -12988,7 +12974,7 @@
       <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="B448" t="n">
@@ -13021,7 +13007,7 @@
       <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="n">
+      <c r="A449" s="1" t="n">
         <v>44681</v>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -13052,7 +13038,7 @@
       <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="1" t="n">
         <v>44712</v>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -13083,7 +13069,7 @@
       <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="n">
+      <c r="A451" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="B451" t="n">
@@ -13116,7 +13102,7 @@
       <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -13147,7 +13133,7 @@
       <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="n">
+      <c r="A453" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -13178,7 +13164,7 @@
       <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B454" t="n">
@@ -13211,7 +13197,7 @@
       <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="n">
+      <c r="A455" s="1" t="n">
         <v>44865</v>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -13242,7 +13228,7 @@
       <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="1" t="n">
         <v>44895</v>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -13273,7 +13259,7 @@
       <c r="K456" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="n">
+      <c r="A457" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="B457" t="n">
@@ -13306,7 +13292,7 @@
       <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="1" t="n">
         <v>44957</v>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -13337,7 +13323,7 @@
       <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="n">
+      <c r="A459" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -13368,7 +13354,7 @@
       <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B460" t="n">
@@ -13401,7 +13387,7 @@
       <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="n">
+      <c r="A461" s="1" t="n">
         <v>45046</v>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -13432,7 +13418,7 @@
       <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -13463,7 +13449,7 @@
       <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="n">
+      <c r="A463" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B463" t="n">
@@ -13496,7 +13482,7 @@
       <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -13527,7 +13513,7 @@
       <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="n">
+      <c r="A465" s="1" t="n">
         <v>45169</v>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -13558,7 +13544,7 @@
       <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="B466" t="n">
@@ -13591,7 +13577,7 @@
       <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="n">
+      <c r="A467" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -13622,7 +13608,7 @@
       <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -13653,7 +13639,7 @@
       <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="n">
+      <c r="A469" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="B469" t="n">
@@ -13686,7 +13672,7 @@
       <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -13717,7 +13703,7 @@
       <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="n">
+      <c r="A471" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -13748,7 +13734,7 @@
       <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="B472" t="n">
@@ -13781,7 +13767,7 @@
       <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
-      <c r="A473" s="2" t="n">
+      <c r="A473" s="1" t="n">
         <v>45412</v>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -13812,7 +13798,7 @@
       <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="n">
+      <c r="A474" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -13843,7 +13829,7 @@
       <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" s="2" t="n">
+      <c r="A475" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="B475" t="n">
@@ -13876,7 +13862,7 @@
       <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" s="2" t="n">
+      <c r="A476" s="1" t="n">
         <v>45504</v>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -13907,7 +13893,7 @@
       <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
-      <c r="A477" s="2" t="n">
+      <c r="A477" s="1" t="n">
         <v>45535</v>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -13938,7 +13924,7 @@
       <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" s="2" t="n">
+      <c r="A478" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="B478" t="n">
@@ -13971,7 +13957,7 @@
       <c r="K478" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" s="2" t="n">
+      <c r="A479" s="1" t="n">
         <v>45596</v>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -14002,7 +13988,7 @@
       <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
-      <c r="A480" s="2" t="n">
+      <c r="A480" s="1" t="n">
         <v>45626</v>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -14033,7 +14019,7 @@
       <c r="K480" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" s="2" t="n">
+      <c r="A481" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="B481" t="n">
@@ -14066,7 +14052,7 @@
       <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" s="2" t="n">
+      <c r="A482" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -14097,7 +14083,7 @@
       <c r="K482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="n">
+      <c r="A483" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -14128,7 +14114,7 @@
       <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" s="2" t="n">
+      <c r="A484" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="B484" t="n">
@@ -14161,7 +14147,7 @@
       <c r="K484" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" s="2" t="n">
+      <c r="A485" s="1" t="n">
         <v>45777</v>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -14192,7 +14178,7 @@
       <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
-      <c r="A486" s="2" t="n">
+      <c r="A486" s="1" t="n">
         <v>45808</v>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -14223,7 +14209,7 @@
       <c r="K486" t="inlineStr"/>
     </row>
     <row r="487">
-      <c r="A487" s="2" t="n">
+      <c r="A487" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B487" t="n">
@@ -14256,7 +14242,7 @@
       <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" s="2" t="n">
+      <c r="A488" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -14287,7 +14273,7 @@
       <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="n">
+      <c r="A489" s="1" t="n">
         <v>45900</v>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -14318,7 +14304,7 @@
       <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="n">
+      <c r="A490" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="B490" t="n">
@@ -14351,7 +14337,7 @@
       <c r="K490" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="n">
+      <c r="A491" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -14382,7 +14368,7 @@
       <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="n">
+      <c r="A492" s="1" t="n">
         <v>45991</v>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -14413,7 +14399,7 @@
       <c r="K492" t="inlineStr"/>
     </row>
     <row r="493">
-      <c r="A493" s="2" t="n">
+      <c r="A493" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="B493" t="n">
@@ -14446,7 +14432,7 @@
       <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" s="2" t="n">
+      <c r="A494" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -14477,7 +14463,7 @@
       <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" s="2" t="n">
+      <c r="A495" s="1" t="n">
         <v>46081</v>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -14508,7 +14494,7 @@
       <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="n">
+      <c r="A496" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B496" t="n">
@@ -14541,7 +14527,7 @@
       <c r="K496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" s="2" t="n">
+      <c r="A497" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -14572,7 +14558,7 @@
       <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
-      <c r="A498" s="2" t="n">
+      <c r="A498" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -14603,7 +14589,7 @@
       <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" s="2" t="n">
+      <c r="A499" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B499" t="n">
@@ -14636,7 +14622,7 @@
       <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="n">
+      <c r="A500" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -14667,7 +14653,7 @@
       <c r="K500" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" s="2" t="n">
+      <c r="A501" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -14696,7 +14682,7 @@
       <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">
-      <c r="A502" s="2" t="n">
+      <c r="A502" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>
@@ -14711,7 +14697,7 @@
       <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr"/>
       <c r="I502" t="n">
-        <v>4.652053771886941</v>
+        <v>4.653007515402251</v>
       </c>
       <c r="J502" t="n">
         <v>4.596689494135473</v>

--- a/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
@@ -12546,7 +12546,7 @@
         <v>4.588024027153121</v>
       </c>
       <c r="F434" t="n">
-        <v>4.455509411433685</v>
+        <v>4.456670177669648</v>
       </c>
       <c r="G434" t="n">
         <v>4.508659285607248</v>
@@ -12672,7 +12672,7 @@
         <v>4.585987366571318</v>
       </c>
       <c r="F438" t="n">
-        <v>4.563305981889393</v>
+        <v>4.562262684976814</v>
       </c>
       <c r="G438" t="n">
         <v>4.613138355637268</v>
@@ -12705,7 +12705,7 @@
         <v>4.604169685654508</v>
       </c>
       <c r="F439" t="n">
-        <v>4.593097604753822</v>
+        <v>4.592084946439436</v>
       </c>
       <c r="G439" t="n">
         <v>4.627909672957581</v>
@@ -12736,7 +12736,7 @@
         <v>4.613138355637268</v>
       </c>
       <c r="F440" t="n">
-        <v>4.628886712605407</v>
+        <v>4.625952725170619</v>
       </c>
       <c r="G440" t="n">
         <v>4.620058798481842</v>
@@ -12767,7 +12767,7 @@
         <v>4.601162164590552</v>
       </c>
       <c r="F441" t="n">
-        <v>4.618086411254637</v>
+        <v>4.620058798481842</v>
       </c>
       <c r="G441" t="n">
         <v>4.625952725170619</v>
@@ -12800,7 +12800,7 @@
         <v>4.60816569496789</v>
       </c>
       <c r="F442" t="n">
-        <v>4.666265285347902</v>
+        <v>4.667205576907544</v>
       </c>
       <c r="G442" t="n">
         <v>4.628886712605407</v>
@@ -12831,7 +12831,7 @@
         <v>4.607168188650764</v>
       </c>
       <c r="F443" t="n">
-        <v>4.68213122712422</v>
+        <v>4.683981366412381</v>
       </c>
       <c r="G443" t="n">
         <v>4.648229675448539</v>
@@ -12862,7 +12862,7 @@
         <v>4.626931677769604</v>
       </c>
       <c r="F444" t="n">
-        <v>4.677490847567717</v>
+        <v>4.678420647727684</v>
       </c>
       <c r="G444" t="n">
         <v>4.623991940228679</v>
@@ -12895,7 +12895,7 @@
         <v>4.611152257665639</v>
       </c>
       <c r="F445" t="n">
-        <v>4.694096395182493</v>
+        <v>4.693181063310805</v>
       </c>
       <c r="G445" t="n">
         <v>4.628886712605407</v>
@@ -12990,7 +12990,7 @@
         <v>4.619073091157083</v>
       </c>
       <c r="F448" t="n">
-        <v>4.783316371371566</v>
+        <v>4.782479200958502</v>
       </c>
       <c r="G448" t="n">
         <v>4.614129927359564</v>
@@ -13085,7 +13085,7 @@
         <v>4.59511985013459</v>
       </c>
       <c r="F451" t="n">
-        <v>4.799090878625398</v>
+        <v>4.798266815950004</v>
       </c>
       <c r="G451" t="n">
         <v>4.611152257665639</v>
@@ -13116,7 +13116,7 @@
         <v>4.601162164590552</v>
       </c>
       <c r="F452" t="n">
-        <v>4.800736969532067</v>
+        <v>4.798266815950004</v>
       </c>
       <c r="G452" t="n">
         <v>4.61512051684126</v>
@@ -13147,7 +13147,7 @@
         <v>4.628886712605407</v>
       </c>
       <c r="F453" t="n">
-        <v>4.828313737302302</v>
+        <v>4.829912458665998</v>
       </c>
       <c r="G453" t="n">
         <v>4.613138355637268</v>
@@ -13180,7 +13180,7 @@
         <v>4.602165676967792</v>
       </c>
       <c r="F454" t="n">
-        <v>4.811371016571989</v>
+        <v>4.812184355372417</v>
       </c>
       <c r="G454" t="n">
         <v>4.612145799724517</v>
@@ -13211,7 +13211,7 @@
         <v>4.590056548178043</v>
       </c>
       <c r="F455" t="n">
-        <v>4.823502180305079</v>
+        <v>4.825108606353353</v>
       </c>
       <c r="G455" t="n">
         <v>4.604169685654508</v>
@@ -13370,7 +13370,7 @@
         <v>4.592084946439436</v>
       </c>
       <c r="F460" t="n">
-        <v>4.848900370910689</v>
+        <v>4.848116364598481</v>
       </c>
       <c r="G460" t="n">
         <v>4.59511985013459</v>
@@ -13432,7 +13432,7 @@
         <v>4.585987366571318</v>
       </c>
       <c r="F462" t="n">
-        <v>4.827513417131532</v>
+        <v>4.826712455935327</v>
       </c>
       <c r="G462" t="n">
         <v>4.594109238628667</v>
@@ -13465,7 +13465,7 @@
         <v>4.588024027153121</v>
       </c>
       <c r="F463" t="n">
-        <v>4.862135285777812</v>
+        <v>4.860587297852597</v>
       </c>
       <c r="G463" t="n">
         <v>4.588024027153121</v>
@@ -13496,7 +13496,7 @@
         <v>4.579852378003801</v>
       </c>
       <c r="F464" t="n">
-        <v>4.86599480426999</v>
+        <v>4.863680881139593</v>
       </c>
       <c r="G464" t="n">
         <v>4.58700621536042</v>
@@ -13527,7 +13527,7 @@
         <v>4.588024027153121</v>
       </c>
       <c r="F465" t="n">
-        <v>4.906015244966153</v>
+        <v>4.908233360478174</v>
       </c>
       <c r="G465" t="n">
         <v>4.582924577040772</v>
@@ -13591,7 +13591,7 @@
         <v>4.582924577040772</v>
       </c>
       <c r="F467" t="n">
-        <v>4.897093252697127</v>
+        <v>4.897839799950911</v>
       </c>
       <c r="G467" t="n">
         <v>4.580877493419047</v>
@@ -13622,7 +13622,7 @@
         <v>4.562262684976814</v>
       </c>
       <c r="F468" t="n">
-        <v>4.906015244966153</v>
+        <v>4.906755163608864</v>
       </c>
       <c r="G468" t="n">
         <v>4.583946549536464</v>
@@ -13686,7 +13686,7 @@
         <v>4.553876891600541</v>
       </c>
       <c r="F470" t="n">
-        <v>4.92870191133357</v>
+        <v>4.927978060415247</v>
       </c>
       <c r="G470" t="n">
         <v>4.580877493419047</v>
@@ -13781,7 +13781,7 @@
         <v>4.544358046591334</v>
       </c>
       <c r="F473" t="n">
-        <v>4.902307417210627</v>
+        <v>4.901564199041894</v>
       </c>
       <c r="G473" t="n">
         <v>4.579852378003801</v>
@@ -13812,7 +13812,7 @@
         <v>4.545420181582317</v>
       </c>
       <c r="F474" t="n">
-        <v>4.894101477840304</v>
+        <v>4.893352133481524</v>
       </c>
       <c r="G474" t="n">
         <v>4.582924577040772</v>
@@ -13845,7 +13845,7 @@
         <v>4.549657476057832</v>
       </c>
       <c r="F475" t="n">
-        <v>4.900820428089049</v>
+        <v>4.900076103529192</v>
       </c>
       <c r="G475" t="n">
         <v>4.578826210648489</v>
@@ -13876,7 +13876,7 @@
         <v>4.534747721691546</v>
       </c>
       <c r="F476" t="n">
-        <v>4.906015244966153</v>
+        <v>4.903050083416319</v>
       </c>
       <c r="G476" t="n">
         <v>4.582924577040772</v>
@@ -13907,7 +13907,7 @@
         <v>4.545420181582317</v>
       </c>
       <c r="F477" t="n">
-        <v>4.903050083416319</v>
+        <v>4.90453376321371</v>
       </c>
       <c r="G477" t="n">
         <v>4.583946549536464</v>
@@ -13940,7 +13940,7 @@
         <v>4.533674184283021</v>
       </c>
       <c r="F478" t="n">
-        <v>4.903050083416319</v>
+        <v>4.90527477843843</v>
       </c>
       <c r="G478" t="n">
         <v>4.591071261608589</v>
@@ -13971,7 +13971,7 @@
         <v>4.539030383483547</v>
       </c>
       <c r="F479" t="n">
-        <v>4.894850261102546</v>
+        <v>4.895598484107897</v>
       </c>
       <c r="G479" t="n">
         <v>4.583946549536464</v>
@@ -14002,7 +14002,7 @@
         <v>4.541164856012179</v>
       </c>
       <c r="F480" t="n">
-        <v>4.934473933130691</v>
+        <v>4.935193098929397</v>
       </c>
       <c r="G480" t="n">
         <v>4.576770711466393</v>
@@ -14035,7 +14035,7 @@
         <v>4.517431271680085</v>
       </c>
       <c r="F481" t="n">
-        <v>4.899331224537582</v>
+        <v>4.900076103529192</v>
       </c>
       <c r="G481" t="n">
         <v>4.584967478670572</v>
@@ -14161,7 +14161,7 @@
         <v>4.540098189244376</v>
       </c>
       <c r="F485" t="n">
-        <v>4.932313327320786</v>
+        <v>4.931592086755803</v>
       </c>
       <c r="G485" t="n">
         <v>4.580877493419047</v>
@@ -14256,7 +14256,7 @@
         <v>4.545420181582317</v>
       </c>
       <c r="F488" t="n">
-        <v>4.940927881671436</v>
+        <v>4.937347498326424</v>
       </c>
       <c r="G488" t="n">
         <v>4.583946549536464</v>
@@ -14287,7 +14287,7 @@
         <v>4.528289141652134</v>
       </c>
       <c r="F489" t="n">
-        <v>4.926528784799256</v>
+        <v>4.929425238670713</v>
       </c>
       <c r="G489" t="n">
         <v>4.579852378003801</v>
@@ -14320,7 +14320,7 @@
         <v>4.547541073151455</v>
       </c>
       <c r="F490" t="n">
-        <v>4.943782987108415</v>
+        <v>4.944495491591711</v>
       </c>
       <c r="G490" t="n">
         <v>4.577798989191959</v>
@@ -14351,7 +14351,7 @@
         <v>4.537961436294641</v>
       </c>
       <c r="F491" t="n">
-        <v>4.959341999708705</v>
+        <v>4.960043507980195</v>
       </c>
       <c r="G491" t="n">
         <v>4.582924577040772</v>
@@ -14382,7 +14382,7 @@
         <v>4.550714000192032</v>
       </c>
       <c r="F492" t="n">
-        <v>4.956531035103055</v>
+        <v>4.957937505095806</v>
       </c>
       <c r="G492" t="n">
         <v>4.585987366571318</v>
@@ -14446,7 +14446,7 @@
         <v>4.537961436294641</v>
       </c>
       <c r="F494" t="n">
-        <v>4.93806460126142</v>
+        <v>4.938781190328272</v>
       </c>
       <c r="G494" t="n">
         <v>4.583946549536464</v>
@@ -14541,7 +14541,7 @@
         <v>4.549657476057832</v>
       </c>
       <c r="F497" t="n">
-        <v>4.963543686562405</v>
+        <v>4.962844630259907</v>
       </c>
       <c r="G497" t="n">
         <v>4.585987366571318</v>
@@ -14572,7 +14572,7 @@
         <v>4.546481189639412</v>
       </c>
       <c r="F498" t="n">
-        <v>4.964242254526545</v>
+        <v>4.964940334834126</v>
       </c>
       <c r="G498" t="n">
         <v>4.581901559048737</v>
@@ -14605,7 +14605,7 @@
         <v>4.536891345234797</v>
       </c>
       <c r="F499" t="n">
-        <v>4.94306997460049</v>
+        <v>4.942356453342962</v>
       </c>
       <c r="G499" t="n">
         <v>4.583946549536464</v>
@@ -14636,7 +14636,7 @@
         <v>4.543294782270004</v>
       </c>
       <c r="F500" t="n">
-        <v>4.92870191133357</v>
+        <v>4.93662988078576</v>
       </c>
       <c r="G500" t="n">
         <v>4.579852378003801</v>
@@ -14666,7 +14666,9 @@
       <c r="E501" t="n">
         <v>4.530446639792155</v>
       </c>
-      <c r="F501" t="inlineStr"/>
+      <c r="F501" t="n">
+        <v>4.906755163608864</v>
+      </c>
       <c r="G501" t="n">
         <v>4.580877493419047</v>
       </c>

--- a/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,13 +48,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,64 +435,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>GDPyoy</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>EURIBOR 3M</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EcSent</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>IPall</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CONSindex</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>retail</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>unemployment</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HICP</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Brent</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>STOXX</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>31078</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -497,7 +511,7 @@
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>31106</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -516,7 +530,7 @@
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>31137</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -535,7 +549,7 @@
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>31167</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -554,7 +568,7 @@
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>31198</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -573,7 +587,7 @@
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>31228</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -592,7 +606,7 @@
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>31259</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -611,7 +625,7 @@
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>31290</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -630,7 +644,7 @@
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>31320</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -649,7 +663,7 @@
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>31351</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -668,7 +682,7 @@
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>31381</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -687,7 +701,7 @@
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>31412</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -706,7 +720,7 @@
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>31443</v>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -725,7 +739,7 @@
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>31471</v>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -744,7 +758,7 @@
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>31502</v>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -763,7 +777,7 @@
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>31532</v>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -782,7 +796,7 @@
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>31563</v>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -801,7 +815,7 @@
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>31593</v>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -820,7 +834,7 @@
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>31624</v>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -839,7 +853,7 @@
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>31655</v>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -858,7 +872,7 @@
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>31685</v>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -877,7 +891,7 @@
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>31716</v>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -896,7 +910,7 @@
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>31746</v>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -915,7 +929,7 @@
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>31777</v>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -934,7 +948,7 @@
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>31808</v>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -953,7 +967,7 @@
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>31836</v>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -972,7 +986,7 @@
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>31867</v>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -991,7 +1005,7 @@
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>31897</v>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1010,7 +1024,7 @@
       <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>31928</v>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1029,7 +1043,7 @@
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>31958</v>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1048,7 +1062,7 @@
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>31989</v>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1067,7 +1081,7 @@
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>32020</v>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1086,7 +1100,7 @@
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>32050</v>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1105,7 +1119,7 @@
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>32081</v>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1124,7 +1138,7 @@
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>32111</v>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1143,7 +1157,7 @@
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>32142</v>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1162,7 +1176,7 @@
       <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>32173</v>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1181,7 +1195,7 @@
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>32202</v>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1200,7 +1214,7 @@
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>32233</v>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1219,7 +1233,7 @@
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>32263</v>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1238,7 +1252,7 @@
       <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>32294</v>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1257,7 +1271,7 @@
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>32324</v>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1276,7 +1290,7 @@
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>32355</v>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1295,7 +1309,7 @@
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>32386</v>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1314,7 +1328,7 @@
       <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>32416</v>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1333,7 +1347,7 @@
       <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>32447</v>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1352,7 +1366,7 @@
       <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>32477</v>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1371,7 +1385,7 @@
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>32508</v>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1390,7 +1404,7 @@
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>32539</v>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1409,7 +1423,7 @@
       <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>32567</v>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1428,7 +1442,7 @@
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>32598</v>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1447,7 +1461,7 @@
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>32628</v>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1466,7 +1480,7 @@
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>32659</v>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1485,7 +1499,7 @@
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>32689</v>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -1504,7 +1518,7 @@
       <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>32720</v>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1523,7 +1537,7 @@
       <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>32751</v>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1542,7 +1556,7 @@
       <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>32781</v>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -1561,7 +1575,7 @@
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>32812</v>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -1580,7 +1594,7 @@
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>32842</v>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -1599,7 +1613,7 @@
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>32873</v>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -1618,7 +1632,7 @@
       <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>32904</v>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -1639,7 +1653,7 @@
       <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>32932</v>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -1660,7 +1674,7 @@
       <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>32963</v>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -1681,7 +1695,7 @@
       <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>32993</v>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -1702,7 +1716,7 @@
       <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>33024</v>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -1723,7 +1737,7 @@
       <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>33054</v>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -1744,7 +1758,7 @@
       <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>33085</v>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -1765,7 +1779,7 @@
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>33116</v>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -1786,7 +1800,7 @@
       <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>33146</v>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -1807,7 +1821,7 @@
       <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>33177</v>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -1828,7 +1842,7 @@
       <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>33207</v>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1849,7 +1863,7 @@
       <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>33238</v>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -1870,7 +1884,7 @@
       <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>33269</v>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1891,7 +1905,7 @@
       <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>33297</v>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -1912,7 +1926,7 @@
       <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>33328</v>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -1933,7 +1947,7 @@
       <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>33358</v>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -1954,7 +1968,7 @@
       <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>33389</v>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -1975,7 +1989,7 @@
       <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>33419</v>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -1996,7 +2010,7 @@
       <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>33450</v>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2017,7 +2031,7 @@
       <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>33481</v>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2038,7 +2052,7 @@
       <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>33511</v>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -2059,7 +2073,7 @@
       <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>33542</v>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2080,7 +2094,7 @@
       <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>33572</v>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2101,7 +2115,7 @@
       <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>33603</v>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -2122,7 +2136,7 @@
       <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>33634</v>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -2143,7 +2157,7 @@
       <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>33663</v>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -2164,7 +2178,7 @@
       <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>33694</v>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -2185,7 +2199,7 @@
       <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>33724</v>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -2206,7 +2220,7 @@
       <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>33755</v>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -2227,7 +2241,7 @@
       <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>33785</v>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -2248,7 +2262,7 @@
       <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>33816</v>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -2269,7 +2283,7 @@
       <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>33847</v>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -2290,7 +2304,7 @@
       <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>33877</v>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -2311,7 +2325,7 @@
       <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>33908</v>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -2332,7 +2346,7 @@
       <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>33938</v>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -2353,7 +2367,7 @@
       <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>33969</v>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -2374,7 +2388,7 @@
       <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>34000</v>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -2395,7 +2409,7 @@
       <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>34028</v>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -2416,7 +2430,7 @@
       <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>34059</v>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -2437,7 +2451,7 @@
       <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>34089</v>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -2458,7 +2472,7 @@
       <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>34120</v>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -2479,7 +2493,7 @@
       <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>34150</v>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -2500,7 +2514,7 @@
       <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>34181</v>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -2521,7 +2535,7 @@
       <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>34212</v>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -2542,7 +2556,7 @@
       <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>34242</v>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -2563,7 +2577,7 @@
       <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>34273</v>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -2584,7 +2598,7 @@
       <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>34303</v>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -2605,7 +2619,7 @@
       <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>34334</v>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -2626,7 +2640,7 @@
       <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>34365</v>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -2649,7 +2663,7 @@
       <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>34393</v>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -2672,7 +2686,7 @@
       <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>34424</v>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -2695,7 +2709,7 @@
       <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>34454</v>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -2718,7 +2732,7 @@
       <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>34485</v>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -2741,7 +2755,7 @@
       <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>34515</v>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -2764,7 +2778,7 @@
       <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>34546</v>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -2787,7 +2801,7 @@
       <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>34577</v>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -2810,7 +2824,7 @@
       <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>34607</v>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -2833,7 +2847,7 @@
       <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>34638</v>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -2856,7 +2870,7 @@
       <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>34668</v>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -2879,7 +2893,7 @@
       <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>34699</v>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -2902,7 +2916,7 @@
       <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>34730</v>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -2927,7 +2941,7 @@
       <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>34758</v>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -2952,7 +2966,7 @@
       <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>34789</v>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -2977,7 +2991,7 @@
       <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>34819</v>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -3002,7 +3016,7 @@
       <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>34850</v>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -3027,7 +3041,7 @@
       <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>34880</v>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -3052,7 +3066,7 @@
       <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>34911</v>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -3077,7 +3091,7 @@
       <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -3102,7 +3116,7 @@
       <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>34972</v>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -3127,7 +3141,7 @@
       <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>35003</v>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -3152,7 +3166,7 @@
       <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>35033</v>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -3177,7 +3191,7 @@
       <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>35064</v>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -3202,7 +3216,7 @@
       <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>35095</v>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -3229,7 +3243,7 @@
       <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>35124</v>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -3256,7 +3270,7 @@
       <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>35155</v>
       </c>
       <c r="B136" t="n">
@@ -3285,7 +3299,7 @@
       <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>35185</v>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -3312,7 +3326,7 @@
       <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>35216</v>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -3339,7 +3353,7 @@
       <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>35246</v>
       </c>
       <c r="B139" t="n">
@@ -3368,7 +3382,7 @@
       <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>35277</v>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -3395,7 +3409,7 @@
       <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>35308</v>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -3422,7 +3436,7 @@
       <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>35338</v>
       </c>
       <c r="B142" t="n">
@@ -3451,7 +3465,7 @@
       <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>35369</v>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -3478,7 +3492,7 @@
       <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>35399</v>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -3505,7 +3519,7 @@
       <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>35430</v>
       </c>
       <c r="B145" t="n">
@@ -3534,7 +3548,7 @@
       <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>35461</v>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -3561,7 +3575,7 @@
       <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>35489</v>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -3588,7 +3602,7 @@
       <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>35520</v>
       </c>
       <c r="B148" t="n">
@@ -3617,7 +3631,7 @@
       <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>35550</v>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -3644,7 +3658,7 @@
       <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>35581</v>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -3671,7 +3685,7 @@
       <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>35611</v>
       </c>
       <c r="B151" t="n">
@@ -3700,7 +3714,7 @@
       <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>35642</v>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -3727,7 +3741,7 @@
       <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>35673</v>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -3754,7 +3768,7 @@
       <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>35703</v>
       </c>
       <c r="B154" t="n">
@@ -3783,7 +3797,7 @@
       <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>35734</v>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -3810,7 +3824,7 @@
       <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>35764</v>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -3837,7 +3851,7 @@
       <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>35795</v>
       </c>
       <c r="B157" t="n">
@@ -3866,7 +3880,7 @@
       <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>35826</v>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -3893,7 +3907,7 @@
       <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>35854</v>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -3920,7 +3934,7 @@
       <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>35885</v>
       </c>
       <c r="B160" t="n">
@@ -3949,7 +3963,7 @@
       <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>35915</v>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -3976,7 +3990,7 @@
       <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>35946</v>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -4003,7 +4017,7 @@
       <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>35976</v>
       </c>
       <c r="B163" t="n">
@@ -4032,7 +4046,7 @@
       <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>36007</v>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -4059,7 +4073,7 @@
       <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>36038</v>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -4086,7 +4100,7 @@
       <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>36068</v>
       </c>
       <c r="B166" t="n">
@@ -4115,7 +4129,7 @@
       <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>36099</v>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -4142,7 +4156,7 @@
       <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>36129</v>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -4169,7 +4183,7 @@
       <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>36160</v>
       </c>
       <c r="B169" t="n">
@@ -4198,7 +4212,7 @@
       <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>36191</v>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -4227,7 +4241,7 @@
       <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>36219</v>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -4256,7 +4270,7 @@
       <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>36250</v>
       </c>
       <c r="B172" t="n">
@@ -4287,7 +4301,7 @@
       <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>36280</v>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -4316,7 +4330,7 @@
       <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>36311</v>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -4345,7 +4359,7 @@
       <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>36341</v>
       </c>
       <c r="B175" t="n">
@@ -4376,7 +4390,7 @@
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>36372</v>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -4405,7 +4419,7 @@
       <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>36403</v>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -4434,7 +4448,7 @@
       <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>36433</v>
       </c>
       <c r="B178" t="n">
@@ -4465,7 +4479,7 @@
       <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>36464</v>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -4494,7 +4508,7 @@
       <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>36494</v>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -4523,7 +4537,7 @@
       <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>36525</v>
       </c>
       <c r="B181" t="n">
@@ -4554,7 +4568,7 @@
       <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>36556</v>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -4585,7 +4599,7 @@
       <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>36585</v>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -4616,7 +4630,7 @@
       <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>36616</v>
       </c>
       <c r="B184" t="n">
@@ -4649,7 +4663,7 @@
       <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>36646</v>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -4680,7 +4694,7 @@
       <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>36677</v>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -4711,7 +4725,7 @@
       <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>36707</v>
       </c>
       <c r="B187" t="n">
@@ -4744,7 +4758,7 @@
       <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>36738</v>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -4775,7 +4789,7 @@
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>36769</v>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -4806,7 +4820,7 @@
       <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>36799</v>
       </c>
       <c r="B190" t="n">
@@ -4839,7 +4853,7 @@
       <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>36830</v>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -4870,7 +4884,7 @@
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>36860</v>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -4901,7 +4915,7 @@
       <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>36891</v>
       </c>
       <c r="B193" t="n">
@@ -4934,7 +4948,7 @@
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>36922</v>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -4965,7 +4979,7 @@
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>36950</v>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -4996,7 +5010,7 @@
       <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>36981</v>
       </c>
       <c r="B196" t="n">
@@ -5029,7 +5043,7 @@
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>37011</v>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -5060,7 +5074,7 @@
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>37042</v>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -5091,7 +5105,7 @@
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>37072</v>
       </c>
       <c r="B199" t="n">
@@ -5124,7 +5138,7 @@
       <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>37103</v>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -5155,7 +5169,7 @@
       <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>37134</v>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -5186,7 +5200,7 @@
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>37164</v>
       </c>
       <c r="B202" t="n">
@@ -5219,7 +5233,7 @@
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>37195</v>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -5250,7 +5264,7 @@
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>37225</v>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -5281,7 +5295,7 @@
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>37256</v>
       </c>
       <c r="B205" t="n">
@@ -5314,7 +5328,7 @@
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>37287</v>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -5345,7 +5359,7 @@
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>37315</v>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -5376,7 +5390,7 @@
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>37346</v>
       </c>
       <c r="B208" t="n">
@@ -5409,7 +5423,7 @@
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>37376</v>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -5440,7 +5454,7 @@
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>37407</v>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -5471,7 +5485,7 @@
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>37437</v>
       </c>
       <c r="B211" t="n">
@@ -5504,7 +5518,7 @@
       <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>37468</v>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -5535,7 +5549,7 @@
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>37499</v>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -5566,7 +5580,7 @@
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>37529</v>
       </c>
       <c r="B214" t="n">
@@ -5599,7 +5613,7 @@
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>37560</v>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -5630,7 +5644,7 @@
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>37590</v>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -5661,7 +5675,7 @@
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>37621</v>
       </c>
       <c r="B217" t="n">
@@ -5694,7 +5708,7 @@
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>37652</v>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -5725,7 +5739,7 @@
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>37680</v>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -5756,7 +5770,7 @@
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>37711</v>
       </c>
       <c r="B220" t="n">
@@ -5789,7 +5803,7 @@
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>37741</v>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -5820,7 +5834,7 @@
       <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>37772</v>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -5851,7 +5865,7 @@
       <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>37802</v>
       </c>
       <c r="B223" t="n">
@@ -5884,7 +5898,7 @@
       <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>37833</v>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -5915,7 +5929,7 @@
       <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>37864</v>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -5946,7 +5960,7 @@
       <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>37894</v>
       </c>
       <c r="B226" t="n">
@@ -5979,7 +5993,7 @@
       <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>37925</v>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -6010,7 +6024,7 @@
       <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>37955</v>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -6041,7 +6055,7 @@
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>37986</v>
       </c>
       <c r="B229" t="n">
@@ -6074,7 +6088,7 @@
       <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>38017</v>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -6105,7 +6119,7 @@
       <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>38046</v>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -6136,7 +6150,7 @@
       <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>38077</v>
       </c>
       <c r="B232" t="n">
@@ -6169,7 +6183,7 @@
       <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>38107</v>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -6200,7 +6214,7 @@
       <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>38138</v>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -6231,7 +6245,7 @@
       <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>38168</v>
       </c>
       <c r="B235" t="n">
@@ -6264,7 +6278,7 @@
       <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>38199</v>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -6295,7 +6309,7 @@
       <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>38230</v>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -6326,7 +6340,7 @@
       <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>38260</v>
       </c>
       <c r="B238" t="n">
@@ -6359,7 +6373,7 @@
       <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>38291</v>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -6390,7 +6404,7 @@
       <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>38321</v>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -6421,7 +6435,7 @@
       <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>38352</v>
       </c>
       <c r="B241" t="n">
@@ -6454,7 +6468,7 @@
       <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>38383</v>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -6485,7 +6499,7 @@
       <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>38411</v>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -6516,7 +6530,7 @@
       <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>38442</v>
       </c>
       <c r="B244" t="n">
@@ -6549,7 +6563,7 @@
       <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>38472</v>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -6580,7 +6594,7 @@
       <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>38503</v>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -6611,7 +6625,7 @@
       <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>38533</v>
       </c>
       <c r="B247" t="n">
@@ -6644,7 +6658,7 @@
       <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>38564</v>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -6675,7 +6689,7 @@
       <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>38595</v>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -6706,7 +6720,7 @@
       <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>38625</v>
       </c>
       <c r="B250" t="n">
@@ -6739,7 +6753,7 @@
       <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>38656</v>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -6770,7 +6784,7 @@
       <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>38686</v>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -6801,7 +6815,7 @@
       <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>38717</v>
       </c>
       <c r="B253" t="n">
@@ -6834,7 +6848,7 @@
       <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -6865,7 +6879,7 @@
       <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -6896,7 +6910,7 @@
       <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B256" t="n">
@@ -6929,7 +6943,7 @@
       <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -6960,7 +6974,7 @@
       <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -6991,7 +7005,7 @@
       <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B259" t="n">
@@ -7024,7 +7038,7 @@
       <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -7055,7 +7069,7 @@
       <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -7086,7 +7100,7 @@
       <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B262" t="n">
@@ -7119,7 +7133,7 @@
       <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -7150,7 +7164,7 @@
       <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -7181,7 +7195,7 @@
       <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B265" t="n">
@@ -7214,7 +7228,7 @@
       <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -7245,7 +7259,7 @@
       <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -7276,7 +7290,7 @@
       <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B268" t="n">
@@ -7309,7 +7323,7 @@
       <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -7340,7 +7354,7 @@
       <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -7371,7 +7385,7 @@
       <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B271" t="n">
@@ -7404,7 +7418,7 @@
       <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -7435,7 +7449,7 @@
       <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -7466,7 +7480,7 @@
       <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B274" t="n">
@@ -7499,7 +7513,7 @@
       <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -7530,7 +7544,7 @@
       <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -7561,7 +7575,7 @@
       <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B277" t="n">
@@ -7594,7 +7608,7 @@
       <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -7625,7 +7639,7 @@
       <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -7656,7 +7670,7 @@
       <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B280" t="n">
@@ -7689,7 +7703,7 @@
       <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -7720,7 +7734,7 @@
       <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -7751,7 +7765,7 @@
       <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B283" t="n">
@@ -7784,7 +7798,7 @@
       <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -7815,7 +7829,7 @@
       <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -7846,7 +7860,7 @@
       <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B286" t="n">
@@ -7879,7 +7893,7 @@
       <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -7910,7 +7924,7 @@
       <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -7941,7 +7955,7 @@
       <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B289" t="n">
@@ -7974,7 +7988,7 @@
       <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -8005,7 +8019,7 @@
       <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -8036,7 +8050,7 @@
       <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B292" t="n">
@@ -8069,7 +8083,7 @@
       <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -8100,7 +8114,7 @@
       <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -8131,7 +8145,7 @@
       <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B295" t="n">
@@ -8164,7 +8178,7 @@
       <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -8195,7 +8209,7 @@
       <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -8226,7 +8240,7 @@
       <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B298" t="n">
@@ -8259,7 +8273,7 @@
       <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -8290,7 +8304,7 @@
       <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -8321,7 +8335,7 @@
       <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B301" t="n">
@@ -8354,7 +8368,7 @@
       <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -8385,7 +8399,7 @@
       <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -8416,7 +8430,7 @@
       <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B304" t="n">
@@ -8449,7 +8463,7 @@
       <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -8480,7 +8494,7 @@
       <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -8511,7 +8525,7 @@
       <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B307" t="n">
@@ -8544,7 +8558,7 @@
       <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -8575,7 +8589,7 @@
       <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -8606,7 +8620,7 @@
       <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B310" t="n">
@@ -8639,7 +8653,7 @@
       <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -8670,7 +8684,7 @@
       <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -8701,7 +8715,7 @@
       <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B313" t="n">
@@ -8734,7 +8748,7 @@
       <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -8765,7 +8779,7 @@
       <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -8796,7 +8810,7 @@
       <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B316" t="n">
@@ -8829,7 +8843,7 @@
       <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -8860,7 +8874,7 @@
       <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -8891,7 +8905,7 @@
       <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B319" t="n">
@@ -8924,7 +8938,7 @@
       <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -8955,7 +8969,7 @@
       <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -8986,7 +9000,7 @@
       <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B322" t="n">
@@ -9019,7 +9033,7 @@
       <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -9050,7 +9064,7 @@
       <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -9081,7 +9095,7 @@
       <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B325" t="n">
@@ -9114,7 +9128,7 @@
       <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -9145,7 +9159,7 @@
       <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -9176,7 +9190,7 @@
       <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B328" t="n">
@@ -9209,7 +9223,7 @@
       <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -9240,7 +9254,7 @@
       <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -9271,7 +9285,7 @@
       <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B331" t="n">
@@ -9304,7 +9318,7 @@
       <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -9335,7 +9349,7 @@
       <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -9366,7 +9380,7 @@
       <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B334" t="n">
@@ -9399,7 +9413,7 @@
       <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -9430,7 +9444,7 @@
       <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -9461,7 +9475,7 @@
       <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B337" t="n">
@@ -9494,7 +9508,7 @@
       <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -9525,7 +9539,7 @@
       <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -9556,7 +9570,7 @@
       <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B340" t="n">
@@ -9589,7 +9603,7 @@
       <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -9620,7 +9634,7 @@
       <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -9651,7 +9665,7 @@
       <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B343" t="n">
@@ -9684,7 +9698,7 @@
       <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -9715,7 +9729,7 @@
       <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -9746,7 +9760,7 @@
       <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B346" t="n">
@@ -9779,7 +9793,7 @@
       <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -9810,7 +9824,7 @@
       <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -9841,7 +9855,7 @@
       <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B349" t="n">
@@ -9874,7 +9888,7 @@
       <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -9905,7 +9919,7 @@
       <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -9936,7 +9950,7 @@
       <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B352" t="n">
@@ -9969,7 +9983,7 @@
       <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -10000,7 +10014,7 @@
       <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -10031,7 +10045,7 @@
       <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B355" t="n">
@@ -10064,7 +10078,7 @@
       <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -10095,7 +10109,7 @@
       <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -10126,7 +10140,7 @@
       <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B358" t="n">
@@ -10159,7 +10173,7 @@
       <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -10190,7 +10204,7 @@
       <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -10221,7 +10235,7 @@
       <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B361" t="n">
@@ -10254,7 +10268,7 @@
       <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -10285,7 +10299,7 @@
       <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -10316,7 +10330,7 @@
       <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B364" t="n">
@@ -10349,7 +10363,7 @@
       <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -10380,7 +10394,7 @@
       <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -10411,7 +10425,7 @@
       <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B367" t="n">
@@ -10444,7 +10458,7 @@
       <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -10475,7 +10489,7 @@
       <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -10506,7 +10520,7 @@
       <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B370" t="n">
@@ -10539,7 +10553,7 @@
       <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -10570,7 +10584,7 @@
       <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -10601,7 +10615,7 @@
       <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B373" t="n">
@@ -10634,7 +10648,7 @@
       <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -10665,7 +10679,7 @@
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -10696,7 +10710,7 @@
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B376" t="n">
@@ -10729,7 +10743,7 @@
       <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -10760,7 +10774,7 @@
       <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -10791,7 +10805,7 @@
       <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B379" t="n">
@@ -10824,7 +10838,7 @@
       <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -10855,7 +10869,7 @@
       <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -10886,7 +10900,7 @@
       <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B382" t="n">
@@ -10919,7 +10933,7 @@
       <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -10950,7 +10964,7 @@
       <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -10981,7 +10995,7 @@
       <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B385" t="n">
@@ -11014,7 +11028,7 @@
       <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -11045,7 +11059,7 @@
       <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -11076,7 +11090,7 @@
       <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B388" t="n">
@@ -11109,7 +11123,7 @@
       <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -11140,7 +11154,7 @@
       <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -11171,7 +11185,7 @@
       <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B391" t="n">
@@ -11204,7 +11218,7 @@
       <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -11235,7 +11249,7 @@
       <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -11266,7 +11280,7 @@
       <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B394" t="n">
@@ -11299,7 +11313,7 @@
       <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -11330,7 +11344,7 @@
       <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -11361,7 +11375,7 @@
       <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B397" t="n">
@@ -11394,7 +11408,7 @@
       <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -11425,7 +11439,7 @@
       <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -11456,7 +11470,7 @@
       <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B400" t="n">
@@ -11489,7 +11503,7 @@
       <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -11520,7 +11534,7 @@
       <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -11551,7 +11565,7 @@
       <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B403" t="n">
@@ -11584,7 +11598,7 @@
       <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -11615,7 +11629,7 @@
       <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -11646,7 +11660,7 @@
       <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B406" t="n">
@@ -11679,7 +11693,7 @@
       <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -11710,7 +11724,7 @@
       <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -11741,7 +11755,7 @@
       <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B409" t="n">
@@ -11774,7 +11788,7 @@
       <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -11805,7 +11819,7 @@
       <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -11836,7 +11850,7 @@
       <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B412" t="n">
@@ -11869,7 +11883,7 @@
       <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -11900,7 +11914,7 @@
       <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -11931,7 +11945,7 @@
       <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B415" t="n">
@@ -11964,7 +11978,7 @@
       <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -11995,7 +12009,7 @@
       <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -12026,7 +12040,7 @@
       <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B418" t="n">
@@ -12059,7 +12073,7 @@
       <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -12090,7 +12104,7 @@
       <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -12121,7 +12135,7 @@
       <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B421" t="n">
@@ -12154,7 +12168,7 @@
       <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -12185,7 +12199,7 @@
       <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -12216,7 +12230,7 @@
       <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B424" t="n">
@@ -12249,7 +12263,7 @@
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -12278,7 +12292,7 @@
       <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -12309,7 +12323,7 @@
       <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B427" t="n">
@@ -12342,7 +12356,7 @@
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -12373,7 +12387,7 @@
       <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -12404,7 +12418,7 @@
       <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B430" t="n">
@@ -12437,7 +12451,7 @@
       <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -12468,7 +12482,7 @@
       <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -12499,7 +12513,7 @@
       <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B433" t="n">
@@ -12532,7 +12546,7 @@
       <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -12563,7 +12577,7 @@
       <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -12594,7 +12608,7 @@
       <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B436" t="n">
@@ -12627,7 +12641,7 @@
       <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -12658,7 +12672,7 @@
       <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -12689,7 +12703,7 @@
       <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B439" t="n">
@@ -12722,7 +12736,7 @@
       <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -12753,7 +12767,7 @@
       <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -12784,7 +12798,7 @@
       <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B442" t="n">
@@ -12817,7 +12831,7 @@
       <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -12848,7 +12862,7 @@
       <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -12879,7 +12893,7 @@
       <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B445" t="n">
@@ -12912,7 +12926,7 @@
       <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -12943,7 +12957,7 @@
       <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -12974,7 +12988,7 @@
       <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B448" t="n">
@@ -13007,7 +13021,7 @@
       <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -13038,7 +13052,7 @@
       <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -13069,7 +13083,7 @@
       <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B451" t="n">
@@ -13102,7 +13116,7 @@
       <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -13133,7 +13147,7 @@
       <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -13164,7 +13178,7 @@
       <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B454" t="n">
@@ -13197,7 +13211,7 @@
       <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -13228,7 +13242,7 @@
       <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -13259,7 +13273,7 @@
       <c r="K456" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B457" t="n">
@@ -13292,7 +13306,7 @@
       <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -13323,7 +13337,7 @@
       <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -13354,7 +13368,7 @@
       <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B460" t="n">
@@ -13387,7 +13401,7 @@
       <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -13418,7 +13432,7 @@
       <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -13449,7 +13463,7 @@
       <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B463" t="n">
@@ -13482,7 +13496,7 @@
       <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -13513,7 +13527,7 @@
       <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -13544,7 +13558,7 @@
       <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B466" t="n">
@@ -13577,7 +13591,7 @@
       <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -13608,7 +13622,7 @@
       <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -13639,7 +13653,7 @@
       <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B469" t="n">
@@ -13672,7 +13686,7 @@
       <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -13703,7 +13717,7 @@
       <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -13734,7 +13748,7 @@
       <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B472" t="n">
@@ -13767,7 +13781,7 @@
       <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -13798,7 +13812,7 @@
       <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -13829,7 +13843,7 @@
       <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B475" t="n">
@@ -13862,7 +13876,7 @@
       <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -13893,7 +13907,7 @@
       <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -13924,7 +13938,7 @@
       <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B478" t="n">
@@ -13957,7 +13971,7 @@
       <c r="K478" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -13988,7 +14002,7 @@
       <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -14019,7 +14033,7 @@
       <c r="K480" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B481" t="n">
@@ -14052,7 +14066,7 @@
       <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -14083,7 +14097,7 @@
       <c r="K482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -14114,7 +14128,7 @@
       <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B484" t="n">
@@ -14147,7 +14161,7 @@
       <c r="K484" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -14178,7 +14192,7 @@
       <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -14209,7 +14223,7 @@
       <c r="K486" t="inlineStr"/>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B487" t="n">
@@ -14242,7 +14256,7 @@
       <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -14273,7 +14287,7 @@
       <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -14304,7 +14318,7 @@
       <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B490" t="n">
@@ -14337,7 +14351,7 @@
       <c r="K490" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -14368,7 +14382,7 @@
       <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -14399,7 +14413,7 @@
       <c r="K492" t="inlineStr"/>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B493" t="n">
@@ -14432,7 +14446,7 @@
       <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -14463,7 +14477,7 @@
       <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -14494,7 +14508,7 @@
       <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B496" t="n">
@@ -14527,7 +14541,7 @@
       <c r="K496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -14558,7 +14572,7 @@
       <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -14589,7 +14603,7 @@
       <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B499" t="n">
@@ -14622,7 +14636,7 @@
       <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -14653,7 +14667,7 @@
       <c r="K500" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -14684,7 +14698,7 @@
       <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>

--- a/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/IT_data_inspect_noreal_sent_levels_auth.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K502"/>
+  <dimension ref="A1:K503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,7 +1562,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>4.712229258281499</v>
+        <v>4.711330381816482</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
@@ -3666,7 +3666,7 @@
         <v>4.3</v>
       </c>
       <c r="D150" t="n">
-        <v>4.624972813284271</v>
+        <v>4.625952725170619</v>
       </c>
       <c r="E150" t="n">
         <v>4.741447804280639</v>
@@ -4193,7 +4193,7 @@
         <v>3.37</v>
       </c>
       <c r="D169" t="n">
-        <v>4.644390899141372</v>
+        <v>4.643428898105181</v>
       </c>
       <c r="E169" t="n">
         <v>4.73356340075649</v>
@@ -4369,7 +4369,7 @@
         <v>2.6266818</v>
       </c>
       <c r="D175" t="n">
-        <v>4.613138355637268</v>
+        <v>4.614129927359564</v>
       </c>
       <c r="E175" t="n">
         <v>4.751864565138895</v>
@@ -5462,7 +5462,7 @@
         <v>3.4671364</v>
       </c>
       <c r="D210" t="n">
-        <v>4.670957926526095</v>
+        <v>4.671893818030999</v>
       </c>
       <c r="E210" t="n">
         <v>4.78164132910387</v>
@@ -6267,7 +6267,7 @@
         <v>4.704110133842995</v>
       </c>
       <c r="H235" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I235" t="n">
         <v>4.192680462942962</v>
@@ -6381,7 +6381,7 @@
         <v>2.1473333</v>
       </c>
       <c r="D239" t="n">
-        <v>4.629862798578463</v>
+        <v>4.628886712605407</v>
       </c>
       <c r="E239" t="n">
         <v>4.766438333584214</v>
@@ -6982,7 +6982,7 @@
         <v>2.889</v>
       </c>
       <c r="D258" t="n">
-        <v>4.710430696645584</v>
+        <v>4.711330381816482</v>
       </c>
       <c r="E258" t="n">
         <v>4.795790545596741</v>
@@ -6994,7 +6994,7 @@
         <v>4.695924549256556</v>
       </c>
       <c r="H258" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I258" t="n">
         <v>4.235554730773624</v>
@@ -7046,7 +7046,7 @@
         <v>3.1021905</v>
       </c>
       <c r="D260" t="n">
-        <v>4.706823839714591</v>
+        <v>4.707726774313183</v>
       </c>
       <c r="E260" t="n">
         <v>4.783316371371566</v>
@@ -7552,7 +7552,7 @@
         <v>4.6385455</v>
       </c>
       <c r="D276" t="n">
-        <v>4.644390899141372</v>
+        <v>4.643428898105181</v>
       </c>
       <c r="E276" t="n">
         <v>4.795790545596741</v>
@@ -7692,7 +7692,7 @@
         <v>4.670957926526095</v>
       </c>
       <c r="H280" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="I280" t="n">
         <v>4.279440045898781</v>
@@ -8578,7 +8578,7 @@
         <v>4.657762636107262</v>
       </c>
       <c r="H308" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I308" t="n">
         <v>4.306764150173334</v>
@@ -8609,7 +8609,7 @@
         <v>4.65586330030361</v>
       </c>
       <c r="H309" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I309" t="n">
         <v>4.308110951723713</v>
@@ -8799,7 +8799,7 @@
         <v>4.654912277882906</v>
       </c>
       <c r="H315" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I315" t="n">
         <v>4.310799125385514</v>
@@ -9212,7 +9212,7 @@
         <v>4.622027303054514</v>
       </c>
       <c r="H328" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="I328" t="n">
         <v>4.369447852467021</v>
@@ -10371,7 +10371,7 @@
         <v>0.0047</v>
       </c>
       <c r="D365" t="n">
-        <v>4.623010104116422</v>
+        <v>4.623991940228679</v>
       </c>
       <c r="E365" t="n">
         <v>4.553876891600541</v>
@@ -10447,7 +10447,7 @@
         <v>4.603168183317418</v>
       </c>
       <c r="H367" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="I367" t="n">
         <v>4.398146016553765</v>
@@ -11321,7 +11321,7 @@
         <v>-0.3295455</v>
       </c>
       <c r="D395" t="n">
-        <v>4.71760561531788</v>
+        <v>4.716711560720999</v>
       </c>
       <c r="E395" t="n">
         <v>4.612145799724517</v>
@@ -11701,7 +11701,7 @@
         <v>-0.3176957</v>
       </c>
       <c r="D407" t="n">
-        <v>4.665324108807838</v>
+        <v>4.664382045619937</v>
       </c>
       <c r="E407" t="n">
         <v>4.623010104116422</v>
@@ -12017,7 +12017,7 @@
         <v>-0.4076818</v>
       </c>
       <c r="D417" t="n">
-        <v>4.612145799724517</v>
+        <v>4.613138355637268</v>
       </c>
       <c r="E417" t="n">
         <v>4.609162207257629</v>
@@ -12300,7 +12300,7 @@
         <v>-0.27195</v>
       </c>
       <c r="D426" t="n">
-        <v>4.027135812528651</v>
+        <v>4.028916756899646</v>
       </c>
       <c r="E426" t="n">
         <v>4.388257184424518</v>
@@ -12364,7 +12364,7 @@
         <v>-0.4441304</v>
       </c>
       <c r="D428" t="n">
-        <v>4.35799005684564</v>
+        <v>4.359269647551265</v>
       </c>
       <c r="E428" t="n">
         <v>4.535820107853298</v>
@@ -12523,7 +12523,7 @@
         <v>-0.5380909</v>
       </c>
       <c r="D433" t="n">
-        <v>4.525044141508807</v>
+        <v>4.523960130562548</v>
       </c>
       <c r="E433" t="n">
         <v>4.562262684976814</v>
@@ -12649,7 +12649,7 @@
         <v>-0.53815</v>
       </c>
       <c r="D437" t="n">
-        <v>4.661550519424199</v>
+        <v>4.662495252607361</v>
       </c>
       <c r="E437" t="n">
         <v>4.602165676967792</v>
@@ -12775,7 +12775,7 @@
         <v>-0.5475909</v>
       </c>
       <c r="D441" t="n">
-        <v>4.769836807543325</v>
+        <v>4.770684624465665</v>
       </c>
       <c r="E441" t="n">
         <v>4.601162164590552</v>
@@ -12839,7 +12839,7 @@
         <v>-0.5498095</v>
       </c>
       <c r="D443" t="n">
-        <v>4.794963757620747</v>
+        <v>4.794136285500715</v>
       </c>
       <c r="E443" t="n">
         <v>4.607168188650764</v>
@@ -12992,7 +12992,7 @@
         <v>44651</v>
       </c>
       <c r="B448" t="n">
-        <v>13.06344020729765</v>
+        <v>13.06358317859354</v>
       </c>
       <c r="C448" t="n">
         <v>-0.4954348</v>
@@ -13087,13 +13087,13 @@
         <v>44742</v>
       </c>
       <c r="B451" t="n">
-        <v>13.07906540350873</v>
+        <v>13.07892400219643</v>
       </c>
       <c r="C451" t="n">
         <v>-0.2392273</v>
       </c>
       <c r="D451" t="n">
-        <v>4.649187071404866</v>
+        <v>4.650143551630823</v>
       </c>
       <c r="E451" t="n">
         <v>4.59511985013459</v>
@@ -13124,7 +13124,7 @@
         <v>0.036619</v>
       </c>
       <c r="D452" t="n">
-        <v>4.609162207257629</v>
+        <v>4.61015772749913</v>
       </c>
       <c r="E452" t="n">
         <v>4.601162164590552</v>
@@ -13155,7 +13155,7 @@
         <v>0.3947391</v>
       </c>
       <c r="D453" t="n">
-        <v>4.604169685654508</v>
+        <v>4.605170185988092</v>
       </c>
       <c r="E453" t="n">
         <v>4.628886712605407</v>
@@ -13182,7 +13182,7 @@
         <v>44834</v>
       </c>
       <c r="B454" t="n">
-        <v>13.08061178427447</v>
+        <v>13.08063493051356</v>
       </c>
       <c r="C454" t="n">
         <v>1.0108636</v>
@@ -13250,7 +13250,7 @@
         <v>1.8252273</v>
       </c>
       <c r="D456" t="n">
-        <v>4.605170185988092</v>
+        <v>4.604169685654508</v>
       </c>
       <c r="E456" t="n">
         <v>4.588024027153121</v>
@@ -13277,7 +13277,7 @@
         <v>44926</v>
       </c>
       <c r="B457" t="n">
-        <v>13.07820415385796</v>
+        <v>13.07818157839005</v>
       </c>
       <c r="C457" t="n">
         <v>2.0634762</v>
@@ -13372,7 +13372,7 @@
         <v>45016</v>
       </c>
       <c r="B460" t="n">
-        <v>13.08428947840824</v>
+        <v>13.08428033685608</v>
       </c>
       <c r="C460" t="n">
         <v>2.9105652</v>
@@ -13467,13 +13467,13 @@
         <v>45107</v>
       </c>
       <c r="B463" t="n">
-        <v>13.08402953486502</v>
+        <v>13.08385744873174</v>
       </c>
       <c r="C463" t="n">
         <v>3.5358636</v>
       </c>
       <c r="D463" t="n">
-        <v>4.612145799724517</v>
+        <v>4.613138355637268</v>
       </c>
       <c r="E463" t="n">
         <v>4.588024027153121</v>
@@ -13535,7 +13535,7 @@
         <v>3.7803043</v>
       </c>
       <c r="D465" t="n">
-        <v>4.604169685654508</v>
+        <v>4.605170185988092</v>
       </c>
       <c r="E465" t="n">
         <v>4.588024027153121</v>
@@ -13562,7 +13562,7 @@
         <v>45199</v>
       </c>
       <c r="B466" t="n">
-        <v>13.08571951731157</v>
+        <v>13.08593173118537</v>
       </c>
       <c r="C466" t="n">
         <v>3.8800476</v>
@@ -13630,7 +13630,7 @@
         <v>3.9716364</v>
       </c>
       <c r="D468" t="n">
-        <v>4.576770711466393</v>
+        <v>4.575741375297279</v>
       </c>
       <c r="E468" t="n">
         <v>4.562262684976814</v>
@@ -13657,13 +13657,13 @@
         <v>45291</v>
       </c>
       <c r="B469" t="n">
-        <v>13.09101924240426</v>
+        <v>13.09098787396001</v>
       </c>
       <c r="C469" t="n">
         <v>3.9348947</v>
       </c>
       <c r="D469" t="n">
-        <v>4.597138014290827</v>
+        <v>4.596129441335942</v>
       </c>
       <c r="E469" t="n">
         <v>4.585987366571318</v>
@@ -13752,7 +13752,7 @@
         <v>45382</v>
       </c>
       <c r="B472" t="n">
-        <v>13.09245721283948</v>
+        <v>13.09238055127736</v>
       </c>
       <c r="C472" t="n">
         <v>3.9231</v>
@@ -13847,7 +13847,7 @@
         <v>45473</v>
       </c>
       <c r="B475" t="n">
-        <v>13.09507049203304</v>
+        <v>13.09489083939935</v>
       </c>
       <c r="C475" t="n">
         <v>3.7245</v>
@@ -13915,7 +13915,7 @@
         <v>3.5475909</v>
       </c>
       <c r="D477" t="n">
-        <v>4.592084946439436</v>
+        <v>4.593097604753822</v>
       </c>
       <c r="E477" t="n">
         <v>4.545420181582317</v>
@@ -13942,13 +13942,13 @@
         <v>45565</v>
       </c>
       <c r="B478" t="n">
-        <v>13.09564520475158</v>
+        <v>13.09592124529679</v>
       </c>
       <c r="C478" t="n">
         <v>3.4337143</v>
       </c>
       <c r="D478" t="n">
-        <v>4.603168183317418</v>
+        <v>4.604169685654508</v>
       </c>
       <c r="E478" t="n">
         <v>4.533674184283021</v>
@@ -13979,7 +13979,7 @@
         <v>3.1666087</v>
       </c>
       <c r="D479" t="n">
-        <v>4.597138014290827</v>
+        <v>4.596129441335942</v>
       </c>
       <c r="E479" t="n">
         <v>4.539030383483547</v>
@@ -14010,7 +14010,7 @@
         <v>3.0067619</v>
       </c>
       <c r="D480" t="n">
-        <v>4.594109238628667</v>
+        <v>4.593097604753822</v>
       </c>
       <c r="E480" t="n">
         <v>4.541164856012179</v>
@@ -14037,13 +14037,13 @@
         <v>45657</v>
       </c>
       <c r="B481" t="n">
-        <v>13.09671710522517</v>
+        <v>13.09669679065508</v>
       </c>
       <c r="C481" t="n">
         <v>2.8246</v>
       </c>
       <c r="D481" t="n">
-        <v>4.585987366571318</v>
+        <v>4.584967478670572</v>
       </c>
       <c r="E481" t="n">
         <v>4.517431271680085</v>
@@ -14074,7 +14074,7 @@
         <v>2.7042727</v>
       </c>
       <c r="D482" t="n">
-        <v>4.602165676967792</v>
+        <v>4.601162164590552</v>
       </c>
       <c r="E482" t="n">
         <v>4.543294782270004</v>
@@ -14105,7 +14105,7 @@
         <v>2.52495</v>
       </c>
       <c r="D483" t="n">
-        <v>4.601162164590552</v>
+        <v>4.600157644164547</v>
       </c>
       <c r="E483" t="n">
         <v>4.534747721691546</v>
@@ -14132,13 +14132,13 @@
         <v>45747</v>
       </c>
       <c r="B484" t="n">
-        <v>13.1006386961453</v>
+        <v>13.10024291400021</v>
       </c>
       <c r="C484" t="n">
         <v>2.4424286</v>
       </c>
       <c r="D484" t="n">
-        <v>4.580877493419047</v>
+        <v>4.581901559048737</v>
       </c>
       <c r="E484" t="n">
         <v>4.533674184283021</v>
@@ -14200,7 +14200,7 @@
         <v>2.0872381</v>
       </c>
       <c r="D486" t="n">
-        <v>4.596129441335942</v>
+        <v>4.597138014290827</v>
       </c>
       <c r="E486" t="n">
         <v>4.535820107853298</v>
@@ -14227,7 +14227,7 @@
         <v>45838</v>
       </c>
       <c r="B487" t="n">
-        <v>13.10033226487841</v>
+        <v>13.10012574388533</v>
       </c>
       <c r="C487" t="n">
         <v>1.983619</v>
@@ -14264,7 +14264,7 @@
         <v>1.9863478</v>
       </c>
       <c r="D488" t="n">
-        <v>4.601162164590552</v>
+        <v>4.602165676967792</v>
       </c>
       <c r="E488" t="n">
         <v>4.545420181582317</v>
@@ -14295,7 +14295,7 @@
         <v>2.0210952</v>
       </c>
       <c r="D489" t="n">
-        <v>4.589040804058207</v>
+        <v>4.590056548178043</v>
       </c>
       <c r="E489" t="n">
         <v>4.528289141652134</v>
@@ -14307,7 +14307,7 @@
         <v>4.579852378003801</v>
       </c>
       <c r="H489" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I489" t="n">
         <v>4.600157644164547</v>
@@ -14322,7 +14322,7 @@
         <v>45930</v>
       </c>
       <c r="B490" t="n">
-        <v>13.1024779666817</v>
+        <v>13.10303518554586</v>
       </c>
       <c r="C490" t="n">
         <v>2.0272727</v>
@@ -14340,7 +14340,7 @@
         <v>4.577798989191959</v>
       </c>
       <c r="H490" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I490" t="n">
         <v>4.612145799724517</v>
@@ -14359,7 +14359,7 @@
         <v>2.0344348</v>
       </c>
       <c r="D491" t="n">
-        <v>4.612145799724517</v>
+        <v>4.61015772749913</v>
       </c>
       <c r="E491" t="n">
         <v>4.537961436294641</v>
@@ -14390,7 +14390,7 @@
         <v>2.04165</v>
       </c>
       <c r="D492" t="n">
-        <v>4.623010104116422</v>
+        <v>4.622027303054514</v>
       </c>
       <c r="E492" t="n">
         <v>4.550714000192032</v>
@@ -14417,7 +14417,7 @@
         <v>46022</v>
       </c>
       <c r="B493" t="n">
-        <v>13.10565394923136</v>
+        <v>13.10569746945628</v>
       </c>
       <c r="C493" t="n">
         <v>2.0484286</v>
@@ -14512,7 +14512,7 @@
         <v>46112</v>
       </c>
       <c r="B496" t="n">
-        <v>13.10888636912838</v>
+        <v>13.10871181744548</v>
       </c>
       <c r="C496" t="n">
         <v>2.1094091</v>
@@ -14561,7 +14561,7 @@
         <v>4.585987366571318</v>
       </c>
       <c r="H497" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I497" t="n">
         <v>4.637637376125593</v>
@@ -14607,13 +14607,13 @@
         <v>46203</v>
       </c>
       <c r="B499" t="n">
-        <v>13.11043774893473</v>
+        <v>13.11034484329248</v>
       </c>
       <c r="C499" t="n">
         <v>2.339</v>
       </c>
       <c r="D499" t="n">
-        <v>4.598145571051127</v>
+        <v>4.599152113662528</v>
       </c>
       <c r="E499" t="n">
         <v>4.536891345234797</v>
@@ -14625,7 +14625,7 @@
         <v>4.583946549536464</v>
       </c>
       <c r="H499" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I499" t="n">
         <v>4.640537329825382</v>
@@ -14644,7 +14644,7 @@
         <v>2.4253913</v>
       </c>
       <c r="D500" t="n">
-        <v>4.601162164590552</v>
+        <v>4.602165676967792</v>
       </c>
       <c r="E500" t="n">
         <v>4.543294782270004</v>
@@ -14656,7 +14656,7 @@
         <v>4.579852378003801</v>
       </c>
       <c r="H500" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I500" t="n">
         <v>4.630837932736669</v>
@@ -14675,7 +14675,7 @@
         <v>2.5131429</v>
       </c>
       <c r="D501" t="n">
-        <v>4.611152257665639</v>
+        <v>4.613138355637268</v>
       </c>
       <c r="E501" t="n">
         <v>4.530446639792155</v>
@@ -14701,17 +14701,21 @@
       <c r="A502" s="2" t="n">
         <v>46295</v>
       </c>
-      <c r="B502" t="inlineStr"/>
+      <c r="B502" t="n">
+        <v>13.11051749112059</v>
+      </c>
       <c r="C502" t="n">
         <v>2.6350455</v>
       </c>
       <c r="D502" t="n">
-        <v>4.603168183317418</v>
+        <v>4.599152113662528</v>
       </c>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="inlineStr"/>
       <c r="G502" t="inlineStr"/>
-      <c r="H502" t="inlineStr"/>
+      <c r="H502" t="n">
+        <v>6.3</v>
+      </c>
       <c r="I502" t="n">
         <v>4.653007515402251</v>
       </c>
@@ -14719,6 +14723,23 @@
         <v>4.596689494135473</v>
       </c>
       <c r="K502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B503" t="inlineStr"/>
+      <c r="C503" t="inlineStr"/>
+      <c r="D503" t="n">
+        <v>4.607168188650764</v>
+      </c>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr"/>
+      <c r="I503" t="inlineStr"/>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
